--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1039">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301051616669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36569008231163</t>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301081418991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690141916275</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424802064896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29174941778183</t>
+    <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114529371262</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
+    <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869655132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313512772321701</t>
+    <t xml:space="preserve">0.313869625329971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313512802124023</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.358822822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.383350729942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.35427314043045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178781509399</t>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.352757453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306301593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060414075851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.372701585292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082119226456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.317455977201462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
+    <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.323543339967728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328246980905533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328247010707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
+    <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.5856614112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,36 +1406,39 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3126,6 +3126,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.648000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.658999979496002</t>
   </si>
 </sst>
 </file>
@@ -15000,7 +15003,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15026,7 +15029,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15052,7 +15055,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15078,7 +15081,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15104,7 +15107,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15130,7 +15133,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15156,7 +15159,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15182,7 +15185,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15208,7 +15211,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15234,7 +15237,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15260,7 +15263,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15286,7 +15289,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15338,7 +15341,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15364,7 +15367,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15442,7 +15445,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15468,7 +15471,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15520,7 +15523,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15546,7 +15549,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15572,7 +15575,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15624,7 +15627,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15650,7 +15653,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15676,7 +15679,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15702,7 +15705,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15728,7 +15731,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15754,7 +15757,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15832,7 +15835,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15858,7 +15861,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15910,7 +15913,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15936,7 +15939,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15962,7 +15965,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16014,7 +16017,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16040,7 +16043,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16066,7 +16069,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16092,7 +16095,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16118,7 +16121,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16170,7 +16173,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16222,7 +16225,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16274,7 +16277,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16300,7 +16303,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16430,7 +16433,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16482,7 +16485,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16508,7 +16511,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16534,7 +16537,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16560,7 +16563,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16586,7 +16589,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16612,7 +16615,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16638,7 +16641,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16664,7 +16667,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16690,7 +16693,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16716,7 +16719,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16742,7 +16745,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16872,7 +16875,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16976,7 +16979,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17002,7 +17005,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17106,7 +17109,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17132,7 +17135,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17236,7 +17239,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17262,7 +17265,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17288,7 +17291,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17314,7 +17317,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17366,7 +17369,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17392,7 +17395,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17418,7 +17421,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17444,7 +17447,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17470,7 +17473,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17496,7 +17499,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17522,7 +17525,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17548,7 +17551,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17574,7 +17577,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17600,7 +17603,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17626,7 +17629,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17652,7 +17655,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17678,7 +17681,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17704,7 +17707,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17730,7 +17733,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17756,7 +17759,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17782,7 +17785,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17808,7 +17811,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17834,7 +17837,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17860,7 +17863,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17886,7 +17889,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17912,7 +17915,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17938,7 +17941,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17964,7 +17967,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18068,7 +18071,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18146,7 +18149,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18172,7 +18175,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18198,7 +18201,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18224,7 +18227,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18250,7 +18253,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18276,7 +18279,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18302,7 +18305,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18328,7 +18331,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18354,7 +18357,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18380,7 +18383,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18406,7 +18409,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18432,7 +18435,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18458,7 +18461,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18484,7 +18487,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18510,7 +18513,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18536,7 +18539,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18562,7 +18565,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18588,7 +18591,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18614,7 +18617,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18640,7 +18643,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18666,7 +18669,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18692,7 +18695,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18718,7 +18721,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18744,7 +18747,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18770,7 +18773,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18796,7 +18799,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18822,7 +18825,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18848,7 +18851,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18874,7 +18877,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18900,7 +18903,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18926,7 +18929,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18952,7 +18955,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18978,7 +18981,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19004,7 +19007,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19030,7 +19033,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19056,7 +19059,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19082,7 +19085,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19108,7 +19111,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19134,7 +19137,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19160,7 +19163,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19186,7 +19189,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19212,7 +19215,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19238,7 +19241,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19264,7 +19267,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19290,7 +19293,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19316,7 +19319,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19342,7 +19345,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19368,7 +19371,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19394,7 +19397,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19420,7 +19423,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19446,7 +19449,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19472,7 +19475,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19498,7 +19501,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19524,7 +19527,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19550,7 +19553,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19576,7 +19579,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19602,7 +19605,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19628,7 +19631,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19654,7 +19657,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19680,7 +19683,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19706,7 +19709,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19732,7 +19735,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21500,7 +21503,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68100,7 +68103,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6495833333</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>1320230</v>
@@ -68121,6 +68124,32 @@
         <v>1037</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494444444</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>745498</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>0.671999990940094</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>0.652999997138977</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>0.654999971389771</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>0.658999979496002</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="1040">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
+    <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.367920368909836</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690141916275</t>
+    <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272134780884</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2888063788414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424802064896</t>
+    <t xml:space="preserve">0.288806408643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749387979507</t>
+    <t xml:space="preserve">0.288984835147858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114529371262</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
+    <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471322774887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869625329971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313512802124023</t>
+    <t xml:space="preserve">0.303166329860687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869595527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063512086868</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.358376741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.352757513523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306301593781</t>
+    <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060414075851</t>
+    <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157930612564</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
+    <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
+    <t xml:space="preserve">0.35231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.357760369777679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
+    <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
+    <t xml:space="preserve">0.338484555482864</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
+    <t xml:space="preserve">0.354071497917175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
+    <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609640955924988</t>
+    <t xml:space="preserve">0.616097271442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609641015529633</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179794788361</t>
+    <t xml:space="preserve">0.609179735183716</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -3129,6 +3129,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.658999979496002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.638999998569489</t>
   </si>
 </sst>
 </file>
@@ -68129,7 +68132,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494444444</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>745498</v>
@@ -68150,6 +68153,32 @@
         <v>1038</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6495717593</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1306226</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.666999995708466</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.63400000333786</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.666999995708466</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.638999998569489</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="1041">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920368909836</t>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321182936429977</t>
+    <t xml:space="preserve">0.33589968085289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3211829662323</t>
   </si>
   <si>
     <t xml:space="preserve">0.316634178161621</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012828111649</t>
+    <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272134780884</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,46 +113,46 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
+    <t xml:space="preserve">0.282830268144608</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
+    <t xml:space="preserve">0.294424742460251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -161,79 +161,79 @@
     <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471382379532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.301471352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.377820700407028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
+    <t xml:space="preserve">0.358376801013947</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579116821289</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351419359445572</t>
+    <t xml:space="preserve">0.351419389247894</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
+    <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.370060473680496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.352318793535233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332212656736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
+    <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3132,6 +3132,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.638999998569489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.644999980926514</t>
   </si>
 </sst>
 </file>
@@ -15006,7 +15009,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15032,7 +15035,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15058,7 +15061,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15084,7 +15087,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15110,7 +15113,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15136,7 +15139,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15162,7 +15165,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15188,7 +15191,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15214,7 +15217,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15240,7 +15243,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15266,7 +15269,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15292,7 +15295,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15344,7 +15347,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15370,7 +15373,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15448,7 +15451,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15474,7 +15477,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15526,7 +15529,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15552,7 +15555,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15578,7 +15581,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15630,7 +15633,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15656,7 +15659,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15682,7 +15685,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15708,7 +15711,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15734,7 +15737,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15760,7 +15763,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15838,7 +15841,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15864,7 +15867,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15916,7 +15919,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15942,7 +15945,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15968,7 +15971,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16020,7 +16023,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16046,7 +16049,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16072,7 +16075,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16098,7 +16101,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16124,7 +16127,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16176,7 +16179,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16228,7 +16231,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16280,7 +16283,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16306,7 +16309,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16436,7 +16439,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16488,7 +16491,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16514,7 +16517,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16540,7 +16543,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16566,7 +16569,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16592,7 +16595,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16618,7 +16621,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16644,7 +16647,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16670,7 +16673,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16696,7 +16699,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16722,7 +16725,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16748,7 +16751,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16878,7 +16881,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16982,7 +16985,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17008,7 +17011,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17112,7 +17115,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17138,7 +17141,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17242,7 +17245,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17268,7 +17271,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17294,7 +17297,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17320,7 +17323,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17372,7 +17375,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17398,7 +17401,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17424,7 +17427,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17450,7 +17453,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17476,7 +17479,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17502,7 +17505,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17528,7 +17531,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17554,7 +17557,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17580,7 +17583,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17606,7 +17609,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17632,7 +17635,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17658,7 +17661,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17684,7 +17687,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17710,7 +17713,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17736,7 +17739,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17762,7 +17765,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17788,7 +17791,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17814,7 +17817,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17840,7 +17843,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17866,7 +17869,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17892,7 +17895,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17918,7 +17921,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17944,7 +17947,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17970,7 +17973,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18074,7 +18077,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18152,7 +18155,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18178,7 +18181,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18204,7 +18207,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18230,7 +18233,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18256,7 +18259,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18282,7 +18285,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18308,7 +18311,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18334,7 +18337,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18360,7 +18363,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18386,7 +18389,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18412,7 +18415,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18438,7 +18441,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18464,7 +18467,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18490,7 +18493,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18516,7 +18519,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18542,7 +18545,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18568,7 +18571,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18594,7 +18597,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18620,7 +18623,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18646,7 +18649,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18672,7 +18675,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18698,7 +18701,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18724,7 +18727,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18750,7 +18753,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18776,7 +18779,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18802,7 +18805,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18828,7 +18831,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18854,7 +18857,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18880,7 +18883,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18906,7 +18909,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18932,7 +18935,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18958,7 +18961,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18984,7 +18987,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19010,7 +19013,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19036,7 +19039,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19062,7 +19065,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19088,7 +19091,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19114,7 +19117,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19140,7 +19143,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19166,7 +19169,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19192,7 +19195,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19218,7 +19221,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19244,7 +19247,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19270,7 +19273,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19296,7 +19299,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19322,7 +19325,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19348,7 +19351,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19374,7 +19377,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19400,7 +19403,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19426,7 +19429,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19452,7 +19455,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19478,7 +19481,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19504,7 +19507,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19530,7 +19533,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19556,7 +19559,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19582,7 +19585,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19608,7 +19611,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19634,7 +19637,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19660,7 +19663,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19686,7 +19689,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19712,7 +19715,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19738,7 +19741,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21506,7 +21509,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68158,7 +68161,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6495717593</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1306226</v>
@@ -68179,6 +68182,32 @@
         <v>1039</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6493287037</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>645915</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.651000022888184</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.638999998569489</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.638999998569489</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.644999980926514</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366360664368</t>
+    <t xml:space="preserve">0.376928627490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366330862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690112113953</t>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36569008231163</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272134780884</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.29174941778183</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114529371262</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.301471322774887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869655132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
+    <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851932048798</t>
+    <t xml:space="preserve">0.354273110628128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.359178781509399</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.358376771211624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306301593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.352757513523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.372701615095139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
+    <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082089424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805374860764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.317455947399139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082119226456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805345058441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
+    <t xml:space="preserve">0.3264020383358</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305824995041</t>
+    <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.32354336977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333532810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328247010707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328246980905533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
+    <t xml:space="preserve">0.326217591762543</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.332397162914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370931863785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378604471683502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517138719559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37860444188118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844259738922</t>
+    <t xml:space="preserve">0.648378193378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.585661470890045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465443134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165138721466</t>
+    <t xml:space="preserve">0.635465383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15012,7 +15012,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15038,7 +15038,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15064,7 +15064,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15090,7 +15090,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15116,7 +15116,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15142,7 +15142,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15168,7 +15168,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15194,7 +15194,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15220,7 +15220,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15246,7 +15246,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15272,7 +15272,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15298,7 +15298,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15350,7 +15350,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15376,7 +15376,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15454,7 +15454,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15480,7 +15480,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15532,7 +15532,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15558,7 +15558,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15584,7 +15584,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15636,7 +15636,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15662,7 +15662,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15688,7 +15688,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15714,7 +15714,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15740,7 +15740,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15766,7 +15766,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15844,7 +15844,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15870,7 +15870,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15922,7 +15922,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15948,7 +15948,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15974,7 +15974,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16026,7 +16026,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16052,7 +16052,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16078,7 +16078,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16104,7 +16104,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16130,7 +16130,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16182,7 +16182,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16234,7 +16234,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16286,7 +16286,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16312,7 +16312,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16442,7 +16442,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16494,7 +16494,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16520,7 +16520,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16546,7 +16546,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16572,7 +16572,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16598,7 +16598,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16624,7 +16624,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16650,7 +16650,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16676,7 +16676,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16702,7 +16702,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16728,7 +16728,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16754,7 +16754,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16884,7 +16884,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16988,7 +16988,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17014,7 +17014,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17118,7 +17118,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17144,7 +17144,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17248,7 +17248,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17274,7 +17274,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17300,7 +17300,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17326,7 +17326,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17378,7 +17378,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17404,7 +17404,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17430,7 +17430,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17456,7 +17456,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17482,7 +17482,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17508,7 +17508,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17534,7 +17534,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17560,7 +17560,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17586,7 +17586,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17612,7 +17612,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17638,7 +17638,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17664,7 +17664,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17690,7 +17690,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17716,7 +17716,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17742,7 +17742,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17768,7 +17768,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17794,7 +17794,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17820,7 +17820,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17846,7 +17846,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17872,7 +17872,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17898,7 +17898,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17924,7 +17924,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17950,7 +17950,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17976,7 +17976,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18080,7 +18080,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18158,7 +18158,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18184,7 +18184,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18210,7 +18210,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18236,7 +18236,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18262,7 +18262,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18288,7 +18288,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18314,7 +18314,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18340,7 +18340,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18366,7 +18366,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18392,7 +18392,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18418,7 +18418,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18444,7 +18444,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18470,7 +18470,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18496,7 +18496,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18522,7 +18522,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18548,7 +18548,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18574,7 +18574,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18600,7 +18600,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18626,7 +18626,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18652,7 +18652,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18678,7 +18678,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18704,7 +18704,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18730,7 +18730,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18756,7 +18756,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18782,7 +18782,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18808,7 +18808,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18834,7 +18834,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18860,7 +18860,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18886,7 +18886,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18912,7 +18912,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18938,7 +18938,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18964,7 +18964,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18990,7 +18990,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19016,7 +19016,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19042,7 +19042,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19068,7 +19068,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19094,7 +19094,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19120,7 +19120,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19146,7 +19146,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19172,7 +19172,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19198,7 +19198,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19224,7 +19224,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19250,7 +19250,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19276,7 +19276,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19302,7 +19302,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19328,7 +19328,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19354,7 +19354,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19380,7 +19380,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19406,7 +19406,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19432,7 +19432,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19458,7 +19458,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19484,7 +19484,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19510,7 +19510,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19536,7 +19536,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19562,7 +19562,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19588,7 +19588,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19614,7 +19614,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19640,7 +19640,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19666,7 +19666,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19692,7 +19692,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19718,7 +19718,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19744,7 +19744,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21512,7 +21512,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68242,7 +68242,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495949074</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>705345</v>
@@ -68263,6 +68263,32 @@
         <v>1014</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493055556</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>240583</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>0.662999987602234</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>0.648999989032745</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>0.662999987602234</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>0.652999997138977</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="1043">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
+    <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36569008231163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
+    <t xml:space="preserve">0.325196444988251</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29174941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166300058365</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869655132294</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
+    <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178781509399</t>
+    <t xml:space="preserve">0.357573866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.379157990217209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
+    <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805345058441</t>
+    <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.349367827177048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
+    <t xml:space="preserve">0.354163706302643</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.341712236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
+    <t xml:space="preserve">0.322620838880539</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
+    <t xml:space="preserve">0.312660068273544</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333532810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328246980905533</t>
+    <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.32621756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
+    <t xml:space="preserve">0.37565353512764</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517108917236</t>
+    <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
+    <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
+    <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465383529663</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -3138,6 +3138,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.66100001335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666000008583069</t>
   </si>
 </sst>
 </file>
@@ -68268,7 +68271,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493055556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>240583</v>
@@ -68289,6 +68292,32 @@
         <v>1014</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493055556</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>594385</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.666000008583069</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="1044">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676573753357</t>
+    <t xml:space="preserve">0.361676633358002</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36569008231163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196444988251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330191254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.325196385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330191224813461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.302720308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382904767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820670604706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.382904708385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.357306241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -3141,6 +3141,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.666000008583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.675000011920929</t>
   </si>
 </sst>
 </file>
@@ -68297,7 +68300,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493055556</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>594385</v>
@@ -68318,6 +68321,32 @@
         <v>1042</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6496412037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>395476</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.658999979496002</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.666999995708466</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="1049">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690141916275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
+    <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424802064896</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500491857529</t>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471382379532</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
+    <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306301593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060414075851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.372701615095139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
+    <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082089424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805374860764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.317455947399139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082119226456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805345058441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
+    <t xml:space="preserve">0.3264020383358</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305824995041</t>
+    <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.32354336977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333532810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328247010707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328246980905533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
+    <t xml:space="preserve">0.326217591762543</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.332397162914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370931863785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378604471683502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517138719559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37860444188118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844259738922</t>
+    <t xml:space="preserve">0.648378193378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.585661470890045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465443134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165138721466</t>
+    <t xml:space="preserve">0.635465383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3156,6 +3156,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.708999991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699000000953674</t>
   </si>
 </sst>
 </file>
@@ -15030,7 +15033,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15056,7 +15059,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15082,7 +15085,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15108,7 +15111,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15134,7 +15137,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15160,7 +15163,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15186,7 +15189,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15212,7 +15215,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15238,7 +15241,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15264,7 +15267,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15290,7 +15293,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15316,7 +15319,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15368,7 +15371,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15394,7 +15397,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15472,7 +15475,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15498,7 +15501,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15550,7 +15553,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15576,7 +15579,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15602,7 +15605,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15654,7 +15657,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15680,7 +15683,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15706,7 +15709,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15732,7 +15735,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15758,7 +15761,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15784,7 +15787,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15862,7 +15865,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15888,7 +15891,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15940,7 +15943,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15966,7 +15969,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15992,7 +15995,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16044,7 +16047,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16070,7 +16073,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16096,7 +16099,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16122,7 +16125,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16148,7 +16151,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16200,7 +16203,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16252,7 +16255,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16304,7 +16307,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16330,7 +16333,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16460,7 +16463,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16512,7 +16515,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16538,7 +16541,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16564,7 +16567,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16590,7 +16593,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16616,7 +16619,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16642,7 +16645,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16668,7 +16671,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16694,7 +16697,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16720,7 +16723,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16746,7 +16749,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16772,7 +16775,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16902,7 +16905,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17006,7 +17009,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17032,7 +17035,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17136,7 +17139,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17162,7 +17165,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17266,7 +17269,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17292,7 +17295,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17318,7 +17321,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17344,7 +17347,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17396,7 +17399,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17422,7 +17425,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17448,7 +17451,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17474,7 +17477,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17500,7 +17503,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17526,7 +17529,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17552,7 +17555,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17578,7 +17581,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17604,7 +17607,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17630,7 +17633,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17656,7 +17659,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17682,7 +17685,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17708,7 +17711,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17734,7 +17737,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17760,7 +17763,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17786,7 +17789,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17812,7 +17815,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17838,7 +17841,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17864,7 +17867,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17890,7 +17893,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17916,7 +17919,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17942,7 +17945,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17968,7 +17971,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17994,7 +17997,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18098,7 +18101,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18176,7 +18179,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18202,7 +18205,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18228,7 +18231,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18254,7 +18257,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18280,7 +18283,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18306,7 +18309,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18332,7 +18335,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18358,7 +18361,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18384,7 +18387,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18410,7 +18413,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18436,7 +18439,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18462,7 +18465,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18488,7 +18491,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18514,7 +18517,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18540,7 +18543,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18566,7 +18569,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18592,7 +18595,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18618,7 +18621,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18644,7 +18647,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18670,7 +18673,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18696,7 +18699,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18722,7 +18725,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18748,7 +18751,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18774,7 +18777,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18800,7 +18803,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18826,7 +18829,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18852,7 +18855,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18878,7 +18881,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18904,7 +18907,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18930,7 +18933,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18956,7 +18959,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18982,7 +18985,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19008,7 +19011,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19034,7 +19037,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19060,7 +19063,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19086,7 +19089,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19112,7 +19115,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19138,7 +19141,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19164,7 +19167,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19190,7 +19193,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19216,7 +19219,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19242,7 +19245,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19268,7 +19271,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19294,7 +19297,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19320,7 +19323,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19346,7 +19349,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19372,7 +19375,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19398,7 +19401,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19424,7 +19427,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19450,7 +19453,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19476,7 +19479,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19502,7 +19505,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19528,7 +19531,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19554,7 +19557,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19580,7 +19583,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19606,7 +19609,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19632,7 +19635,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19658,7 +19661,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19684,7 +19687,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19710,7 +19713,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19736,7 +19739,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19762,7 +19765,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21530,7 +21533,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68442,7 +68445,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909837963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>2194164</v>
@@ -68463,6 +68466,32 @@
         <v>1047</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6912152778</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>2461491</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="1052">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920339107513</t>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301051616669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.362301081418991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690141916275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.330191254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979644775391</t>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
     <t xml:space="preserve">0.28283029794693</t>
@@ -131,73 +131,73 @@
     <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.294424802064896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471322774887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313512802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007607936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736692428589</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
+    <t xml:space="preserve">0.383350729942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806327581406</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
+    <t xml:space="preserve">0.352757453918457</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306271791458</t>
+    <t xml:space="preserve">0.353292763233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306301593781</t>
   </si>
   <si>
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157990217209</t>
+    <t xml:space="preserve">0.370060414075851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
+    <t xml:space="preserve">0.372701585292816</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
+    <t xml:space="preserve">0.368920415639877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
   </si>
   <si>
     <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
+    <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633890628815</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.33783882856369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082119226456</t>
+    <t xml:space="preserve">0.323082089424133</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349367827177048</t>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.354163736104965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341712236404419</t>
+    <t xml:space="preserve">0.341620028018951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326309859752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426558256149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620838880539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.326309829950333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426528453827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312660068273544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305795192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311829835176468</t>
+    <t xml:space="preserve">0.319761246442795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312660098075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305824995041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
     <t xml:space="preserve">0.309892654418945</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
+    <t xml:space="preserve">0.323543339967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
     <t xml:space="preserve">0.338300049304962</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387358665466</t>
+    <t xml:space="preserve">0.325387388467789</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
+    <t xml:space="preserve">0.332397192716599</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,49 +683,49 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429829359055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.375653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429799556732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370931863785</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37860444188118</t>
+    <t xml:space="preserve">0.378604471683502</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
+    <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531818389893</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.430714637041092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
+    <t xml:space="preserve">0.547846794128418</t>
   </si>
   <si>
     <t xml:space="preserve">0.542774081230164</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
     <t xml:space="preserve">0.596267998218536</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
+    <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
     <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.642844259738922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
+    <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
     <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622553646564484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942273616791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.622553706169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942214012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607796967029572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
+    <t xml:space="preserve">0.607797026634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.627165138721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,36 +1406,39 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3165,6 +3165,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.690999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689000010490417</t>
   </si>
 </sst>
 </file>
@@ -15039,7 +15042,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15065,7 +15068,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15091,7 +15094,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15117,7 +15120,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15143,7 +15146,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15169,7 +15172,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15195,7 +15198,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15221,7 +15224,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15247,7 +15250,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15273,7 +15276,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15299,7 +15302,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15325,7 +15328,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15377,7 +15380,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15403,7 +15406,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15481,7 +15484,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15507,7 +15510,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15559,7 +15562,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15585,7 +15588,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15611,7 +15614,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15663,7 +15666,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15689,7 +15692,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15715,7 +15718,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15741,7 +15744,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15767,7 +15770,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15793,7 +15796,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15871,7 +15874,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15897,7 +15900,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15949,7 +15952,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15975,7 +15978,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16001,7 +16004,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16053,7 +16056,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16079,7 +16082,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16105,7 +16108,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16131,7 +16134,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16157,7 +16160,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16209,7 +16212,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16261,7 +16264,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16313,7 +16316,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16339,7 +16342,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16469,7 +16472,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16521,7 +16524,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16547,7 +16550,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16573,7 +16576,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16599,7 +16602,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16625,7 +16628,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16651,7 +16654,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16677,7 +16680,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16703,7 +16706,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16729,7 +16732,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16755,7 +16758,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16781,7 +16784,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16911,7 +16914,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17015,7 +17018,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17041,7 +17044,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17145,7 +17148,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17171,7 +17174,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17275,7 +17278,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17301,7 +17304,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17327,7 +17330,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17353,7 +17356,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17405,7 +17408,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17431,7 +17434,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17457,7 +17460,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17483,7 +17486,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17509,7 +17512,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17535,7 +17538,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17561,7 +17564,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17587,7 +17590,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17613,7 +17616,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17639,7 +17642,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17665,7 +17668,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17691,7 +17694,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17717,7 +17720,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17743,7 +17746,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17769,7 +17772,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17795,7 +17798,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17821,7 +17824,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17847,7 +17850,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17873,7 +17876,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17899,7 +17902,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17925,7 +17928,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17951,7 +17954,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17977,7 +17980,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18003,7 +18006,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18107,7 +18110,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18185,7 +18188,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18211,7 +18214,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18237,7 +18240,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18263,7 +18266,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18289,7 +18292,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18315,7 +18318,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18341,7 +18344,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18367,7 +18370,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18393,7 +18396,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18419,7 +18422,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18445,7 +18448,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18471,7 +18474,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18497,7 +18500,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18523,7 +18526,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18549,7 +18552,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18575,7 +18578,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18601,7 +18604,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18627,7 +18630,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18653,7 +18656,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18679,7 +18682,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18705,7 +18708,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18731,7 +18734,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18757,7 +18760,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18783,7 +18786,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18809,7 +18812,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18835,7 +18838,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18861,7 +18864,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18887,7 +18890,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18913,7 +18916,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18939,7 +18942,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18965,7 +18968,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18991,7 +18994,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19017,7 +19020,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19043,7 +19046,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19069,7 +19072,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19095,7 +19098,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19121,7 +19124,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19147,7 +19150,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19173,7 +19176,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19199,7 +19202,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19225,7 +19228,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19251,7 +19254,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19277,7 +19280,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19303,7 +19306,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19329,7 +19332,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19355,7 +19358,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19381,7 +19384,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19407,7 +19410,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19433,7 +19436,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19459,7 +19462,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19485,7 +19488,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19511,7 +19514,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19537,7 +19540,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19563,7 +19566,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19589,7 +19592,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19615,7 +19618,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19641,7 +19644,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19667,7 +19670,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19693,7 +19696,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19719,7 +19722,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19745,7 +19748,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19771,7 +19774,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21539,7 +21542,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68529,7 +68532,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6912962963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>939505</v>
@@ -68550,6 +68553,32 @@
         <v>1050</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6912037037</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>547292</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>0.689000010490417</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1053">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690141916275</t>
+    <t xml:space="preserve">0.368366330862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36569008231163</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325999289751053</t>
+    <t xml:space="preserve">0.316634207963943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661195278168</t>
+    <t xml:space="preserve">0.324661165475845</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311014920473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.311014890670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424802064896</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
@@ -140,46 +140,46 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304146736860275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304146707057953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.303166329860687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
+    <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993936538696</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350729942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.383350759744644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.358376741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306301593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060414075851</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.372701615095139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
+    <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082089424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805374860764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.317455947399139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082119226456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805345058441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
+    <t xml:space="preserve">0.3264020383358</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305824995041</t>
+    <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.32354336977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333532810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328247010707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328246980905533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
+    <t xml:space="preserve">0.326217591762543</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.332397162914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370931863785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378604471683502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517138719559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37860444188118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844259738922</t>
+    <t xml:space="preserve">0.648378193378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.585661470890045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465443134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165138721466</t>
+    <t xml:space="preserve">0.635465383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3168,6 +3168,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.689000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.689999997615814</t>
   </si>
 </sst>
 </file>
@@ -15042,7 +15045,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15068,7 +15071,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15094,7 +15097,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15120,7 +15123,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15146,7 +15149,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15172,7 +15175,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15198,7 +15201,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15224,7 +15227,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15250,7 +15253,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15276,7 +15279,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15302,7 +15305,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15328,7 +15331,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15380,7 +15383,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15406,7 +15409,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15484,7 +15487,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15510,7 +15513,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15562,7 +15565,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15588,7 +15591,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15614,7 +15617,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15666,7 +15669,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15692,7 +15695,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15718,7 +15721,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15744,7 +15747,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15770,7 +15773,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15796,7 +15799,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15874,7 +15877,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15900,7 +15903,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15952,7 +15955,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15978,7 +15981,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16004,7 +16007,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16056,7 +16059,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16082,7 +16085,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16108,7 +16111,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16134,7 +16137,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16160,7 +16163,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16212,7 +16215,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16264,7 +16267,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16316,7 +16319,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16342,7 +16345,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16472,7 +16475,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16524,7 +16527,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16550,7 +16553,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16576,7 +16579,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16602,7 +16605,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16628,7 +16631,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16654,7 +16657,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16680,7 +16683,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16706,7 +16709,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16732,7 +16735,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16758,7 +16761,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16784,7 +16787,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16914,7 +16917,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17018,7 +17021,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17044,7 +17047,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17148,7 +17151,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17174,7 +17177,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17278,7 +17281,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17304,7 +17307,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17330,7 +17333,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17356,7 +17359,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17408,7 +17411,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17434,7 +17437,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17460,7 +17463,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17486,7 +17489,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17512,7 +17515,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17538,7 +17541,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17564,7 +17567,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17590,7 +17593,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17616,7 +17619,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17642,7 +17645,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17668,7 +17671,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17694,7 +17697,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17720,7 +17723,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17746,7 +17749,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17772,7 +17775,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17798,7 +17801,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17824,7 +17827,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17850,7 +17853,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17876,7 +17879,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17902,7 +17905,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17928,7 +17931,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17954,7 +17957,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17980,7 +17983,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18006,7 +18009,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18110,7 +18113,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18188,7 +18191,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18214,7 +18217,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18240,7 +18243,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18266,7 +18269,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18292,7 +18295,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18318,7 +18321,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18344,7 +18347,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18370,7 +18373,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18396,7 +18399,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18422,7 +18425,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18448,7 +18451,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18474,7 +18477,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18500,7 +18503,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18526,7 +18529,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18552,7 +18555,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18578,7 +18581,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18604,7 +18607,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18630,7 +18633,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18656,7 +18659,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18682,7 +18685,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18708,7 +18711,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18734,7 +18737,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18760,7 +18763,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18786,7 +18789,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18812,7 +18815,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18838,7 +18841,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18864,7 +18867,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18890,7 +18893,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18916,7 +18919,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18942,7 +18945,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18968,7 +18971,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18994,7 +18997,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19020,7 +19023,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19046,7 +19049,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19072,7 +19075,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19098,7 +19101,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19124,7 +19127,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19150,7 +19153,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19176,7 +19179,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19202,7 +19205,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19228,7 +19231,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19254,7 +19257,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19280,7 +19283,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19306,7 +19309,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19332,7 +19335,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19358,7 +19361,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19384,7 +19387,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19410,7 +19413,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19436,7 +19439,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19462,7 +19465,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19488,7 +19491,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19514,7 +19517,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19540,7 +19543,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19566,7 +19569,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19592,7 +19595,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19618,7 +19621,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19644,7 +19647,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19670,7 +19673,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19696,7 +19699,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19722,7 +19725,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19748,7 +19751,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19774,7 +19777,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21542,7 +21545,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68558,7 +68561,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6912037037</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>547292</v>
@@ -68567,7 +68570,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="D2503" t="n">
-        <v>0.689999997615814</v>
+        <v>0.689000010490417</v>
       </c>
       <c r="E2503" t="n">
         <v>0.689999997615814</v>
@@ -68579,6 +68582,32 @@
         <v>1051</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912268518</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>692236</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.676999986171722</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.689000010490417</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -53,19 +53,19 @@
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366330862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301051616669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36569008231163</t>
+    <t xml:space="preserve">0.368366360664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301081418991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690141916275</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634207963943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.316634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661165475845</t>
+    <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311014890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.311014920473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424772262573</t>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424802064896</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
@@ -140,46 +140,46 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
+    <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304146707057953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304146736860275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471352577209</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736722230911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993906736374</t>
+    <t xml:space="preserve">0.358822822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736692428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.383350729942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573926448822</t>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.358376771211624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
+    <t xml:space="preserve">0.352757453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306301593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060414075851</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.372701585292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082119226456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.317455977201462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
+    <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.323543339967728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328246980905533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328247010707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
+    <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.5856614112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,36 +1406,39 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">0.689000010490417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689999997615814</t>
+    <t xml:space="preserve">0.685999989509583</t>
   </si>
 </sst>
 </file>
@@ -15045,7 +15045,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15071,7 +15071,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15097,7 +15097,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15123,7 +15123,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15513,7 +15513,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15617,7 +15617,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15721,7 +15721,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15903,7 +15903,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16007,7 +16007,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16111,7 +16111,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16267,7 +16267,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16319,7 +16319,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16475,7 +16475,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16527,7 +16527,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16579,7 +16579,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16917,7 +16917,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17021,7 +17021,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17047,7 +17047,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17151,7 +17151,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17177,7 +17177,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17281,7 +17281,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17307,7 +17307,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17333,7 +17333,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17463,7 +17463,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18113,7 +18113,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18217,7 +18217,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18243,7 +18243,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21545,7 +21545,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68587,22 +68587,22 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912268518</v>
+        <v>45966.6912152778</v>
       </c>
       <c r="B2504" t="n">
-        <v>692236</v>
+        <v>276145</v>
       </c>
       <c r="C2504" t="n">
-        <v>0.690999984741211</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D2504" t="n">
-        <v>0.676999986171722</v>
+        <v>0.677999973297119</v>
       </c>
       <c r="E2504" t="n">
-        <v>0.689000010490417</v>
+        <v>0.683000028133392</v>
       </c>
       <c r="F2504" t="n">
-        <v>0.689999997615814</v>
+        <v>0.685999989509583</v>
       </c>
       <c r="G2504" t="s">
         <v>1052</v>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="1054">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690141916275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
+    <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424802064896</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500491857529</t>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471382379532</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
+    <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306301593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060414075851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.372701615095139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
+    <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082089424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805374860764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.317455947399139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082119226456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805345058441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
+    <t xml:space="preserve">0.3264020383358</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305824995041</t>
+    <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.32354336977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333532810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328247010707855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328246980905533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
+    <t xml:space="preserve">0.326217591762543</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.332397162914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370931863785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378604471683502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517138719559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37860444188118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844259738922</t>
+    <t xml:space="preserve">0.648378193378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.585661470890045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465443134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165138721466</t>
+    <t xml:space="preserve">0.635465383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3170,7 +3170,10 @@
     <t xml:space="preserve">0.689000010490417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.685999989509583</t>
+    <t xml:space="preserve">0.689999997615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674000024795532</t>
   </si>
 </sst>
 </file>
@@ -15045,7 +15048,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15071,7 +15074,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15097,7 +15100,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15123,7 +15126,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15149,7 +15152,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15175,7 +15178,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15201,7 +15204,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15227,7 +15230,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15253,7 +15256,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15279,7 +15282,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15305,7 +15308,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15331,7 +15334,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15383,7 +15386,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15409,7 +15412,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15487,7 +15490,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15513,7 +15516,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15565,7 +15568,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15591,7 +15594,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15617,7 +15620,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15669,7 +15672,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15695,7 +15698,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15721,7 +15724,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15747,7 +15750,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15773,7 +15776,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15799,7 +15802,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15877,7 +15880,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15903,7 +15906,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15955,7 +15958,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15981,7 +15984,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16007,7 +16010,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16059,7 +16062,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16085,7 +16088,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16111,7 +16114,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16137,7 +16140,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16163,7 +16166,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16215,7 +16218,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16267,7 +16270,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16319,7 +16322,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16345,7 +16348,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16475,7 +16478,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16527,7 +16530,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16553,7 +16556,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16579,7 +16582,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16605,7 +16608,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16631,7 +16634,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16657,7 +16660,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16683,7 +16686,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16709,7 +16712,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16735,7 +16738,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16761,7 +16764,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16787,7 +16790,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16917,7 +16920,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17021,7 +17024,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17047,7 +17050,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17151,7 +17154,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17177,7 +17180,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17281,7 +17284,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17307,7 +17310,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17333,7 +17336,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17359,7 +17362,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17411,7 +17414,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17437,7 +17440,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17463,7 +17466,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17489,7 +17492,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17515,7 +17518,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17541,7 +17544,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17567,7 +17570,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17593,7 +17596,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17619,7 +17622,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17645,7 +17648,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17671,7 +17674,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17697,7 +17700,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17723,7 +17726,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17749,7 +17752,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17775,7 +17778,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17801,7 +17804,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17827,7 +17830,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17853,7 +17856,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17879,7 +17882,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17905,7 +17908,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17931,7 +17934,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17957,7 +17960,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17983,7 +17986,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18009,7 +18012,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18113,7 +18116,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18191,7 +18194,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18217,7 +18220,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18243,7 +18246,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18269,7 +18272,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18295,7 +18298,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18321,7 +18324,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18347,7 +18350,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18373,7 +18376,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18399,7 +18402,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18425,7 +18428,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18451,7 +18454,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18477,7 +18480,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18503,7 +18506,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18529,7 +18532,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18555,7 +18558,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18581,7 +18584,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18607,7 +18610,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18633,7 +18636,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18659,7 +18662,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18685,7 +18688,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18711,7 +18714,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18737,7 +18740,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18763,7 +18766,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18789,7 +18792,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18815,7 +18818,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18841,7 +18844,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18867,7 +18870,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18893,7 +18896,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18919,7 +18922,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18945,7 +18948,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18971,7 +18974,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18997,7 +19000,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19023,7 +19026,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19049,7 +19052,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19075,7 +19078,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19101,7 +19104,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19127,7 +19130,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19153,7 +19156,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19179,7 +19182,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19205,7 +19208,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19231,7 +19234,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19257,7 +19260,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19283,7 +19286,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19309,7 +19312,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19335,7 +19338,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19361,7 +19364,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19387,7 +19390,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19413,7 +19416,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19439,7 +19442,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19465,7 +19468,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19491,7 +19494,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19517,7 +19520,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19543,7 +19546,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19569,7 +19572,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19595,7 +19598,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19621,7 +19624,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19647,7 +19650,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19673,7 +19676,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19699,7 +19702,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19725,7 +19728,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19751,7 +19754,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19777,7 +19780,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21545,7 +21548,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68587,27 +68590,53 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45966.6912152778</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
-        <v>276145</v>
+        <v>692236</v>
       </c>
       <c r="C2504" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.676999986171722</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.689000010490417</v>
+      </c>
+      <c r="F2504" t="n">
         <v>0.689999997615814</v>
-      </c>
-      <c r="D2504" t="n">
-        <v>0.677999973297119</v>
-      </c>
-      <c r="E2504" t="n">
-        <v>0.683000028133392</v>
-      </c>
-      <c r="F2504" t="n">
-        <v>0.685999989509583</v>
       </c>
       <c r="G2504" t="s">
         <v>1052</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45967.6910069444</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>313650</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301051616669</t>
+    <t xml:space="preserve">0.365868479013443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450531482697</t>
+    <t xml:space="preserve">0.325999289751053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272164583206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450561285019</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205820083618</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -140,103 +140,103 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749387979507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512802124023</t>
+    <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.335007607936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350729942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.354273170232773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.379157900810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.372701585292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082119226456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.317455977201462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
+    <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.323543339967728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328246980905533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328247010707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
+    <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.5856614112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,36 +1406,39 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">0.689999997615814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674000024795532</t>
+    <t xml:space="preserve">0.679000020027161</t>
   </si>
 </sst>
 </file>
@@ -15048,7 +15048,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15074,7 +15074,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15100,7 +15100,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15126,7 +15126,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15152,7 +15152,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15178,7 +15178,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15204,7 +15204,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15230,7 +15230,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15256,7 +15256,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15282,7 +15282,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15308,7 +15308,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15334,7 +15334,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15386,7 +15386,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15412,7 +15412,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15490,7 +15490,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15516,7 +15516,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15568,7 +15568,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15594,7 +15594,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15620,7 +15620,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15672,7 +15672,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15698,7 +15698,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15724,7 +15724,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15750,7 +15750,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15776,7 +15776,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15802,7 +15802,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15880,7 +15880,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15906,7 +15906,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15958,7 +15958,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15984,7 +15984,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16010,7 +16010,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16062,7 +16062,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16088,7 +16088,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16114,7 +16114,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16140,7 +16140,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16166,7 +16166,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16218,7 +16218,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16270,7 +16270,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16322,7 +16322,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16348,7 +16348,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16478,7 +16478,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16530,7 +16530,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16556,7 +16556,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16582,7 +16582,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16608,7 +16608,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16634,7 +16634,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16660,7 +16660,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16686,7 +16686,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16712,7 +16712,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16738,7 +16738,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16764,7 +16764,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16790,7 +16790,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16920,7 +16920,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17024,7 +17024,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17050,7 +17050,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17154,7 +17154,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17180,7 +17180,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17284,7 +17284,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17310,7 +17310,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17336,7 +17336,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17362,7 +17362,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17414,7 +17414,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17440,7 +17440,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17466,7 +17466,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17492,7 +17492,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17518,7 +17518,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17544,7 +17544,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17570,7 +17570,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17596,7 +17596,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17622,7 +17622,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17648,7 +17648,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17674,7 +17674,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17700,7 +17700,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17726,7 +17726,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17752,7 +17752,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17778,7 +17778,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17804,7 +17804,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17830,7 +17830,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17882,7 +17882,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17908,7 +17908,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17934,7 +17934,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17960,7 +17960,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17986,7 +17986,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18012,7 +18012,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18116,7 +18116,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18194,7 +18194,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18220,7 +18220,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18246,7 +18246,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18272,7 +18272,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18298,7 +18298,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18324,7 +18324,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18350,7 +18350,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18376,7 +18376,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18402,7 +18402,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18428,7 +18428,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18454,7 +18454,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18480,7 +18480,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18506,7 +18506,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18532,7 +18532,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18558,7 +18558,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18584,7 +18584,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18610,7 +18610,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18636,7 +18636,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18662,7 +18662,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18688,7 +18688,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18714,7 +18714,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18740,7 +18740,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18766,7 +18766,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18792,7 +18792,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18818,7 +18818,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18844,7 +18844,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18870,7 +18870,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18896,7 +18896,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18922,7 +18922,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18948,7 +18948,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18974,7 +18974,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19000,7 +19000,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19026,7 +19026,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19052,7 +19052,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19078,7 +19078,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19104,7 +19104,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19130,7 +19130,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19156,7 +19156,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19182,7 +19182,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19208,7 +19208,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19234,7 +19234,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19260,7 +19260,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19286,7 +19286,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19312,7 +19312,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19338,7 +19338,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19364,7 +19364,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19390,7 +19390,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19416,7 +19416,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19442,7 +19442,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19468,7 +19468,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19494,7 +19494,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19520,7 +19520,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19546,7 +19546,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19572,7 +19572,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19598,7 +19598,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19624,7 +19624,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19650,7 +19650,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19676,7 +19676,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19702,7 +19702,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19728,7 +19728,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19754,7 +19754,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19780,7 +19780,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21548,7 +21548,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68616,22 +68616,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6910069444</v>
+        <v>45968.6910069444</v>
       </c>
       <c r="B2505" t="n">
-        <v>313650</v>
+        <v>430497</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.704999983310699</v>
+        <v>0.681999981403351</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.674000024795532</v>
+        <v>0.671000003814697</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.704999983310699</v>
+        <v>0.675999999046326</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.674000024795532</v>
+        <v>0.679000020027161</v>
       </c>
       <c r="G2505" t="s">
         <v>1053</v>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1056">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -3171,6 +3171,12 @@
   </si>
   <si>
     <t xml:space="preserve">0.689999997615814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.685999989509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.674000024795532</t>
   </si>
   <si>
     <t xml:space="preserve">0.679000020027161</t>
@@ -68616,27 +68622,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6910069444</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>430497</v>
+        <v>276145</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.681999981403351</v>
+        <v>0.689999997615814</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.671000003814697</v>
+        <v>0.677999973297119</v>
       </c>
       <c r="E2505" t="n">
-        <v>0.675999999046326</v>
+        <v>0.683000028133392</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.679000020027161</v>
+        <v>0.685999989509583</v>
       </c>
       <c r="G2505" t="s">
         <v>1053</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>313650</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>430497</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>0.671000003814697</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>0.675999999046326</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>0.679000020027161</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6910069444</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>325513</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.676999986171722</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="1057">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868479013443</t>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.335899740457535</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272164583206</t>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450561285019</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311014920473099</t>
+    <t xml:space="preserve">0.311014950275421</t>
   </si>
   <si>
     <t xml:space="preserve">0.307358235120773</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335573911667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
   </si>
   <si>
     <t xml:space="preserve">0.290500491857529</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820730209351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757453918457</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465999364853</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157900810242</t>
+    <t xml:space="preserve">0.370060414075851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -3180,6 +3180,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.679000020027161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.691999971866608</t>
   </si>
 </sst>
 </file>
@@ -68700,7 +68703,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6910069444</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>325513</v>
@@ -68721,6 +68724,32 @@
         <v>1036</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.69125</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>555826</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="1058">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
+    <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984724283218</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899740457535</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634178161621</t>
+    <t xml:space="preserve">0.316634207963943</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999289751053</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.321272164583206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014950275421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
+    <t xml:space="preserve">0.330191284418106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014920473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205820083618</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">0.293979585170746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
+    <t xml:space="preserve">0.282830327749252</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
@@ -143,46 +143,46 @@
     <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749387979507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335573911667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
+    <t xml:space="preserve">0.303166329860687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382904708385468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820730209351</t>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38290473818779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273170232773</t>
+    <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178721904755</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.358376741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060414075851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157900810242</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
+    <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
+    <t xml:space="preserve">0.35231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.357760369777679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
+    <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
+    <t xml:space="preserve">0.338484555482864</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
+    <t xml:space="preserve">0.354071497917175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
+    <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609640955924988</t>
+    <t xml:space="preserve">0.616097271442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609641015529633</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179794788361</t>
+    <t xml:space="preserve">0.609179735183716</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -3183,6 +3183,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.691999971866608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698000013828278</t>
   </si>
 </sst>
 </file>
@@ -68729,7 +68732,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.69125</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>555826</v>
@@ -68750,6 +68753,32 @@
         <v>1056</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6912962963</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>302619</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="1063">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -68,28 +68,28 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321182936429977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316634207963943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272164583206</t>
+    <t xml:space="preserve">0.33589968085289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3211829662323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191284418106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.330191254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,67 +113,67 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830327749252</t>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.294424742460251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
@@ -182,31 +182,31 @@
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
@@ -215,43 +215,43 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.357573866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.358376801013947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351419359445572</t>
+    <t xml:space="preserve">0.351419389247894</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157900810242</t>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060473680496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.352318793535233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332212656736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
+    <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3198,6 +3198,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.666999995708466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.657999992370605</t>
   </si>
 </sst>
 </file>
@@ -15072,7 +15075,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15098,7 +15101,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15124,7 +15127,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15150,7 +15153,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15176,7 +15179,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15202,7 +15205,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15228,7 +15231,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15254,7 +15257,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15280,7 +15283,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15306,7 +15309,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15332,7 +15335,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15358,7 +15361,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15410,7 +15413,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15436,7 +15439,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15514,7 +15517,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15540,7 +15543,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15592,7 +15595,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15618,7 +15621,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15644,7 +15647,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15696,7 +15699,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15722,7 +15725,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15748,7 +15751,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15774,7 +15777,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15800,7 +15803,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15826,7 +15829,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15904,7 +15907,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15930,7 +15933,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15982,7 +15985,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16008,7 +16011,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16034,7 +16037,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16086,7 +16089,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16112,7 +16115,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16138,7 +16141,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16164,7 +16167,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16190,7 +16193,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16242,7 +16245,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16294,7 +16297,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16346,7 +16349,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16372,7 +16375,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16502,7 +16505,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16554,7 +16557,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16580,7 +16583,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16606,7 +16609,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16632,7 +16635,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16658,7 +16661,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16684,7 +16687,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16710,7 +16713,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16736,7 +16739,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16762,7 +16765,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16788,7 +16791,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16814,7 +16817,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16944,7 +16947,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17048,7 +17051,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17074,7 +17077,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17178,7 +17181,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17204,7 +17207,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17308,7 +17311,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17334,7 +17337,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17360,7 +17363,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17386,7 +17389,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17438,7 +17441,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17464,7 +17467,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17490,7 +17493,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17516,7 +17519,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17542,7 +17545,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17568,7 +17571,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17594,7 +17597,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17620,7 +17623,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17646,7 +17649,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17672,7 +17675,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17698,7 +17701,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17724,7 +17727,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17750,7 +17753,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17776,7 +17779,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17802,7 +17805,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17828,7 +17831,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17854,7 +17857,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17880,7 +17883,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17906,7 +17909,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17932,7 +17935,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17958,7 +17961,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17984,7 +17987,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18010,7 +18013,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18036,7 +18039,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18140,7 +18143,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18218,7 +18221,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18244,7 +18247,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18270,7 +18273,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18296,7 +18299,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18322,7 +18325,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18348,7 +18351,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18374,7 +18377,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18400,7 +18403,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18426,7 +18429,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18452,7 +18455,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18478,7 +18481,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18504,7 +18507,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18530,7 +18533,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18556,7 +18559,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18582,7 +18585,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18608,7 +18611,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18634,7 +18637,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18660,7 +18663,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18686,7 +18689,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18712,7 +18715,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18738,7 +18741,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18764,7 +18767,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18790,7 +18793,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18816,7 +18819,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18842,7 +18845,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18868,7 +18871,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18894,7 +18897,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18920,7 +18923,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18946,7 +18949,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18972,7 +18975,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18998,7 +19001,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19024,7 +19027,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19050,7 +19053,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19076,7 +19079,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19102,7 +19105,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19128,7 +19131,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19154,7 +19157,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19180,7 +19183,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19206,7 +19209,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19232,7 +19235,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19258,7 +19261,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19284,7 +19287,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19310,7 +19313,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19336,7 +19339,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19362,7 +19365,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19388,7 +19391,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19414,7 +19417,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19440,7 +19443,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19466,7 +19469,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19492,7 +19495,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19518,7 +19521,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19544,7 +19547,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19570,7 +19573,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19596,7 +19599,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19622,7 +19625,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19648,7 +19651,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19674,7 +19677,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19700,7 +19703,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19726,7 +19729,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19752,7 +19755,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19778,7 +19781,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19804,7 +19807,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21572,7 +21575,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68874,7 +68877,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6912962963</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>265049</v>
@@ -68895,6 +68898,32 @@
         <v>1061</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.691099537</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>758553</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.651000022888184</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="1064">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.367920368909836</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301051616669</t>
+    <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3211829662323</t>
+    <t xml:space="preserve">0.335899710655212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
     <t xml:space="preserve">0.316634178161621</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012857913971</t>
+    <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272134780884</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,46 +113,46 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424742460251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984805345535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749387979507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
+    <t xml:space="preserve">0.294424772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984835147858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -161,79 +161,79 @@
     <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.301203727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720278501511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.301471382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736722230911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993906736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
+    <t xml:space="preserve">0.358822822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736692428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350789546967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
+    <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376801013947</t>
+    <t xml:space="preserve">0.358376741409302</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579116821289</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351419389247894</t>
+    <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060473680496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157960414886</t>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251045465469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.341251015663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.33783882856369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
+    <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.35231876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163736104965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
+    <t xml:space="preserve">0.357760369777679</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
+    <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212656736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332212686538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305795192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.312660098075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305824995041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.338484555482864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071497917175</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837958097458</t>
+    <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
+    <t xml:space="preserve">0.332397192716599</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.375653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
+    <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370931863785</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37860444188118</t>
+    <t xml:space="preserve">0.378604471683502</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.642844259738922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609640955924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.609641015529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019712924957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179794788361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.627165138721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019772529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,36 +1406,39 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3201,6 +3201,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.657999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.700999975204468</t>
   </si>
 </sst>
 </file>
@@ -15075,7 +15078,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15101,7 +15104,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15127,7 +15130,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15153,7 +15156,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15179,7 +15182,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15205,7 +15208,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15231,7 +15234,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15257,7 +15260,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15283,7 +15286,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15309,7 +15312,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15335,7 +15338,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15361,7 +15364,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15413,7 +15416,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15439,7 +15442,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15517,7 +15520,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15543,7 +15546,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15595,7 +15598,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15621,7 +15624,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15647,7 +15650,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15699,7 +15702,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15725,7 +15728,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15751,7 +15754,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15777,7 +15780,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15803,7 +15806,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15829,7 +15832,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15907,7 +15910,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15933,7 +15936,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15985,7 +15988,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16011,7 +16014,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16037,7 +16040,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16089,7 +16092,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16115,7 +16118,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16141,7 +16144,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16167,7 +16170,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16193,7 +16196,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16245,7 +16248,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16297,7 +16300,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16349,7 +16352,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16375,7 +16378,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16505,7 +16508,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16557,7 +16560,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16583,7 +16586,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16609,7 +16612,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16635,7 +16638,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16661,7 +16664,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16687,7 +16690,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16713,7 +16716,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16739,7 +16742,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16765,7 +16768,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16791,7 +16794,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16817,7 +16820,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16947,7 +16950,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17051,7 +17054,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17077,7 +17080,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17181,7 +17184,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17207,7 +17210,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17311,7 +17314,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17337,7 +17340,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17363,7 +17366,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17389,7 +17392,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17441,7 +17444,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17467,7 +17470,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17493,7 +17496,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17519,7 +17522,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17545,7 +17548,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17571,7 +17574,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17597,7 +17600,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17623,7 +17626,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17649,7 +17652,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17675,7 +17678,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17701,7 +17704,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17727,7 +17730,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17753,7 +17756,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17779,7 +17782,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17805,7 +17808,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17831,7 +17834,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17857,7 +17860,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17883,7 +17886,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17909,7 +17912,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17935,7 +17938,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17961,7 +17964,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17987,7 +17990,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18013,7 +18016,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18039,7 +18042,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18143,7 +18146,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18221,7 +18224,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18247,7 +18250,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18273,7 +18276,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18299,7 +18302,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18325,7 +18328,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18351,7 +18354,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18377,7 +18380,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18403,7 +18406,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18429,7 +18432,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18455,7 +18458,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18481,7 +18484,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18507,7 +18510,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18533,7 +18536,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18559,7 +18562,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18585,7 +18588,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18611,7 +18614,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18637,7 +18640,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18663,7 +18666,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18689,7 +18692,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18715,7 +18718,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18741,7 +18744,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18767,7 +18770,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18793,7 +18796,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18819,7 +18822,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18845,7 +18848,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18871,7 +18874,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18897,7 +18900,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18923,7 +18926,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18949,7 +18952,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18975,7 +18978,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19001,7 +19004,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19027,7 +19030,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19053,7 +19056,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19079,7 +19082,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19105,7 +19108,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19131,7 +19134,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19157,7 +19160,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19183,7 +19186,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19209,7 +19212,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19235,7 +19238,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19261,7 +19264,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19287,7 +19290,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19313,7 +19316,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19339,7 +19342,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19365,7 +19368,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19391,7 +19394,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19417,7 +19420,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19443,7 +19446,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19469,7 +19472,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19495,7 +19498,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19521,7 +19524,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19547,7 +19550,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19573,7 +19576,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19599,7 +19602,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19625,7 +19628,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19651,7 +19654,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19677,7 +19680,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19703,7 +19706,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19729,7 +19732,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19755,7 +19758,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19781,7 +19784,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19807,7 +19810,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21575,7 +21578,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -68903,7 +68906,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.691099537</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>758553</v>
@@ -68924,6 +68927,32 @@
         <v>1062</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6910069444</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>4043898</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="1065">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920368909836</t>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012828111649</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673698186874</t>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749358177185</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500432252884</t>
+    <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869595527649</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
+    <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063512086868</t>
+    <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806327581406</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376741409302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306271791458</t>
+    <t xml:space="preserve">0.357306301593781</t>
   </si>
   <si>
     <t xml:space="preserve">0.362122625112534</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
+    <t xml:space="preserve">0.372701585292816</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
+    <t xml:space="preserve">0.345862418413162</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082119226456</t>
+    <t xml:space="preserve">0.323082089424133</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
+    <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.357760399580002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
+    <t xml:space="preserve">0.331843703985214</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318470686674118</t>
+    <t xml:space="preserve">0.322620868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31847071647644</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32354336977005</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323543339967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
+    <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071497917175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440450668335</t>
+    <t xml:space="preserve">0.354071468114853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440480470657</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
+    <t xml:space="preserve">0.372609376907349</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609641015529633</t>
+    <t xml:space="preserve">0.616097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179735183716</t>
+    <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -3204,6 +3204,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.700999975204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.707000017166138</t>
   </si>
 </sst>
 </file>
@@ -68932,7 +68935,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910069444</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>4043898</v>
@@ -68953,6 +68956,32 @@
         <v>1063</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6909837963</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>1280748</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>0.712000012397766</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>0.681999981403351</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>0.707000017166138</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="1066">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920339107513</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634178161621</t>
+    <t xml:space="preserve">0.316634207963943</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999289751053</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.321272164583206</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191254615784</t>
+    <t xml:space="preserve">0.330191284418106</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671576023102</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830327749252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749358177185</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289876013994217</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
+    <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.357573926448822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306301593781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
+    <t xml:space="preserve">0.379157900810242</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
+    <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
+    <t xml:space="preserve">0.35231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.357760369777679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
+    <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
+    <t xml:space="preserve">0.338484555482864</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
+    <t xml:space="preserve">0.354071497917175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
+    <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609640955924988</t>
+    <t xml:space="preserve">0.616097271442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609641015529633</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179794788361</t>
+    <t xml:space="preserve">0.609179735183716</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -3207,6 +3207,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.707000017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.725000023841858</t>
   </si>
 </sst>
 </file>
@@ -68961,7 +68964,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6909837963</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>1280748</v>
@@ -68982,6 +68985,32 @@
         <v>1064</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6925810185</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>2044388</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.37692865729332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920339107513</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634178161621</t>
+    <t xml:space="preserve">0.316634207963943</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999289751053</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.321272164583206</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.330191284418106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,43 +113,43 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830327749252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289876013994217</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
+    <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178721904755</t>
@@ -242,10 +242,10 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.358376741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
+    <t xml:space="preserve">0.379157900810242</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251045465469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.341251015663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.33783882856369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
+    <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163706302643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.35231876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163736104965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
+    <t xml:space="preserve">0.357760369777679</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
+    <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212656736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332212686538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305795192719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.312660098075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305824995041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.338484555482864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071497917175</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837958097458</t>
+    <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
+    <t xml:space="preserve">0.332397192716599</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.375653505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
+    <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370931863785</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37860444188118</t>
+    <t xml:space="preserve">0.378604471683502</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.642844259738922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609640955924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.609641015529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019712924957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179794788361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.627165138721466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019772529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,34 +1406,37 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15087,7 +15087,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15113,7 +15113,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15139,7 +15139,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15165,7 +15165,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15191,7 +15191,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15217,7 +15217,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15243,7 +15243,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15269,7 +15269,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15295,7 +15295,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15321,7 +15321,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15347,7 +15347,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15373,7 +15373,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15425,7 +15425,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15451,7 +15451,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15529,7 +15529,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15555,7 +15555,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15607,7 +15607,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15633,7 +15633,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15659,7 +15659,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15711,7 +15711,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15737,7 +15737,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15763,7 +15763,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15789,7 +15789,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15815,7 +15815,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15841,7 +15841,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15919,7 +15919,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15945,7 +15945,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15997,7 +15997,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16023,7 +16023,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16049,7 +16049,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16101,7 +16101,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16127,7 +16127,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16153,7 +16153,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16179,7 +16179,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16205,7 +16205,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16257,7 +16257,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16309,7 +16309,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16361,7 +16361,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16387,7 +16387,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16517,7 +16517,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16569,7 +16569,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16595,7 +16595,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16621,7 +16621,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16647,7 +16647,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16673,7 +16673,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16699,7 +16699,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16725,7 +16725,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16751,7 +16751,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16777,7 +16777,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16803,7 +16803,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16829,7 +16829,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16959,7 +16959,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17063,7 +17063,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17089,7 +17089,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17193,7 +17193,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17219,7 +17219,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17323,7 +17323,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17349,7 +17349,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17375,7 +17375,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17401,7 +17401,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17453,7 +17453,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17479,7 +17479,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17505,7 +17505,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17531,7 +17531,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17557,7 +17557,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17583,7 +17583,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17609,7 +17609,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17635,7 +17635,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17661,7 +17661,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17687,7 +17687,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17713,7 +17713,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17739,7 +17739,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17765,7 +17765,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17791,7 +17791,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17817,7 +17817,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17843,7 +17843,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17869,7 +17869,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17895,7 +17895,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17921,7 +17921,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17947,7 +17947,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17973,7 +17973,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17999,7 +17999,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18025,7 +18025,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18051,7 +18051,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18155,7 +18155,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18233,7 +18233,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18259,7 +18259,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18285,7 +18285,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18311,7 +18311,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18337,7 +18337,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18363,7 +18363,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18389,7 +18389,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18415,7 +18415,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18441,7 +18441,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18467,7 +18467,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18493,7 +18493,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18519,7 +18519,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18545,7 +18545,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18571,7 +18571,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18597,7 +18597,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18623,7 +18623,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18649,7 +18649,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18675,7 +18675,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18701,7 +18701,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18727,7 +18727,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18753,7 +18753,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18779,7 +18779,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18805,7 +18805,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18831,7 +18831,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18857,7 +18857,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18883,7 +18883,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18909,7 +18909,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18935,7 +18935,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18961,7 +18961,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18987,7 +18987,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19013,7 +19013,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19039,7 +19039,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19065,7 +19065,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19091,7 +19091,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19117,7 +19117,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19143,7 +19143,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19169,7 +19169,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19195,7 +19195,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19221,7 +19221,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19247,7 +19247,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19273,7 +19273,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19299,7 +19299,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19325,7 +19325,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19351,7 +19351,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19377,7 +19377,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19403,7 +19403,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19429,7 +19429,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19455,7 +19455,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19481,7 +19481,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19507,7 +19507,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19533,7 +19533,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19559,7 +19559,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19585,7 +19585,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19611,7 +19611,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19637,7 +19637,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19663,7 +19663,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19689,7 +19689,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19715,7 +19715,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19741,7 +19741,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19767,7 +19767,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19793,7 +19793,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19819,7 +19819,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21587,7 +21587,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -69045,7 +69045,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912268518</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>1256988</v>
@@ -69066,6 +69066,32 @@
         <v>1047</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.691087963</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>656400</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>0.714999973773956</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>0.703000009059906</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>0.714999973773956</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>0.712000012397766</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -69129,7 +69129,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.691099537</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>1853536</v>
@@ -69150,6 +69150,32 @@
         <v>1068</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6922106482</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>1362146</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="1070">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
+    <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984724283218</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
+    <t xml:space="preserve">0.368366330862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
+    <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
+    <t xml:space="preserve">0.325196444988251</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205849885941</t>
@@ -125,43 +125,43 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29174941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.290857315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471352577209</t>
+    <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007667541504</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
+    <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
@@ -206,22 +206,22 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382904708385468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
+    <t xml:space="preserve">0.379157990217209</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -3219,6 +3219,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.708000004291534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.720000028610229</t>
   </si>
 </sst>
 </file>
@@ -69155,7 +69158,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6922106482</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>1362146</v>
@@ -69176,6 +69179,32 @@
         <v>1068</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6912268518</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>530873</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>0.722000002861023</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.321272164583206</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">0.294424742460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
+    <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166329860687</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736692428589</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382904708385468</t>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063571691513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.362122684717178</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
@@ -69262,7 +69262,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6911111111</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>215438</v>
@@ -69271,7 +69271,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="D2528" t="n">
-        <v>0.705999970436096</v>
+        <v>0.704999983310699</v>
       </c>
       <c r="E2528" t="n">
         <v>0.707000017166138</v>
@@ -69283,6 +69283,32 @@
         <v>1069</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6910532407</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>457121</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.37692865729332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.36569008231163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198314905167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205849885941</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29174941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114559173584</t>
+    <t xml:space="preserve">0.294424742460251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335573911667</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500491857529</t>
+    <t xml:space="preserve">0.290054470300674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.301203727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166329860687</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229486942291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.313512742519379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -203,31 +203,31 @@
     <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993966341019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382904708385468</t>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353203535079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354273170232773</t>
+    <t xml:space="preserve">0.383350789546967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063571691513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353203564882278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.355432868003845</t>
+    <t xml:space="preserve">0.355432897806168</t>
   </si>
   <si>
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292793035507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060414075851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.353292763233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306301593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060473680496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -69320,7 +69320,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6911805556</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>427008</v>
@@ -69341,6 +69341,32 @@
         <v>1058</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6911574074</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>1103901</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>0.717000007629395</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
+    <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36569008231163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.325999289751053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,34 +101,34 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.330191224813461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,22 +137,22 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29174941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869655132294</t>
+    <t xml:space="preserve">0.301471352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
+    <t xml:space="preserve">0.328229546546936</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
+    <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178781509399</t>
+    <t xml:space="preserve">0.357573866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306241989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.357306271791458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.379157990217209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
+    <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805345058441</t>
+    <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.349367827177048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
+    <t xml:space="preserve">0.354163706302643</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.341712236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
+    <t xml:space="preserve">0.322620838880539</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
+    <t xml:space="preserve">0.312660068273544</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333532810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328246980905533</t>
+    <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.32621756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
+    <t xml:space="preserve">0.37565353512764</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517108917236</t>
+    <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
+    <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
+    <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465383529663</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -69479,7 +69479,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6911805556</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>401262</v>
@@ -69500,6 +69500,32 @@
         <v>1067</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6909953704</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>903024</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="1074">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
+    <t xml:space="preserve">0.37692865729332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272104978561</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
+    <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671605825424</t>
@@ -110,58 +110,58 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29174941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
+    <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
@@ -197,25 +197,25 @@
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.370149672031403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -3231,6 +3231,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.702000021934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.703999996185303</t>
   </si>
 </sst>
 </file>
@@ -69505,7 +69508,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6909953704</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>903024</v>
@@ -69526,6 +69529,32 @@
         <v>1048</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6910300926</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>518554</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>0.707000017166138</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301051616669</t>
+    <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
     <t xml:space="preserve">0.36569008231163</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634207963943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325999289751053</t>
+    <t xml:space="preserve">0.316634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272164583206</t>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191254615784</t>
+    <t xml:space="preserve">0.330191224813461</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671576023102</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">0.301114529371262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.294335573911667</t>
   </si>
   <si>
     <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
+    <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166329860687</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993906736374</t>
+    <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820700407028</t>
+    <t xml:space="preserve">0.382904708385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820730209351</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063571691513</t>
+    <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806327581406</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122684717178</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.39658984541893</t>
@@ -69557,7 +69557,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6912847222</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>360676</v>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
+    <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671605825424</t>
@@ -113,55 +113,55 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229546546936</t>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471382379532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313512802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.383350759744644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.352757483720779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -69699,10 +69699,10 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.691099537</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>86934</v>
+        <v>157649</v>
       </c>
       <c r="C2544" t="n">
         <v>0.717999994754791</v>
@@ -69720,6 +69720,32 @@
         <v>1076</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6911342593</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>516109</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>0.708999991416931</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="1077">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272164583206</t>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">0.294424742460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
+    <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">0.290500462055206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720248699188</t>
+    <t xml:space="preserve">0.301203727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166329860687</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
+    <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736692428589</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.370149672031403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063571691513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122684717178</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
@@ -3240,6 +3240,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.714999973773956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.718999981880188</t>
   </si>
 </sst>
 </file>
@@ -69748,7 +69751,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6910416667</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>239859</v>
@@ -69769,6 +69772,32 @@
         <v>1070</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6911111111</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>579402</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>0.72299998998642</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>0.717999994754791</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>0.718999981880188</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.365868479013443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301081418991</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696359395981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830327749252</t>
   </si>
   <si>
     <t xml:space="preserve">0.2888063788414</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289876013994217</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.301203697919846</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
+    <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.370149672031403</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">0.377820730209351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353203564882278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354273170232773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851932048798</t>
+    <t xml:space="preserve">0.353203594684601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35427314043045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344908028841019</t>
+    <t xml:space="preserve">0.344908058643341</t>
   </si>
   <si>
     <t xml:space="preserve">0.352757483720779</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157900810242</t>
+    <t xml:space="preserve">0.370060473680496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697610139847</t>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697580337524</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
+    <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
+    <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313918113708</t>
+    <t xml:space="preserve">0.36430898308754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32372784614563</t>
+    <t xml:space="preserve">0.323727816343307</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
+    <t xml:space="preserve">0.35231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341620028018951</t>
+    <t xml:space="preserve">0.357760369777679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
+    <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
+    <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.312106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484525680542</t>
+    <t xml:space="preserve">0.338484555482864</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
+    <t xml:space="preserve">0.354071497917175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333473205566</t>
+    <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32612532377243</t>
+    <t xml:space="preserve">0.331751435995102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326125353574753</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897642850876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.322897613048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
+    <t xml:space="preserve">0.324558049440384</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
+    <t xml:space="preserve">0.353241264820099</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
+    <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
+    <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.547846734523773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267998218536</t>
+    <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
+    <t xml:space="preserve">0.634543001651764</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609640955924988</t>
+    <t xml:space="preserve">0.616097271442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609641015529633</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
+    <t xml:space="preserve">0.628087520599365</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942214012146</t>
+    <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
+    <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179794788361</t>
+    <t xml:space="preserve">0.609179735183716</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -69832,7 +69832,7 @@
     </row>
     <row r="2549">
       <c r="A2549" s="1" t="n">
-        <v>46035.6909722222</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
         <v>298178</v>
@@ -69853,6 +69853,32 @@
         <v>1072</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.6911574074</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>464209</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>0.693000018596649</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.365868479013443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
+    <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301081418991</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696359395981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830327749252</t>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.2888063788414</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289876013994217</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203697919846</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.335007607936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993906736374</t>
+    <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.370149672031403</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">0.377820730209351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.383350729942322</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353203594684601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.353203564882278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354273170232773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344908058643341</t>
+    <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
     <t xml:space="preserve">0.352757483720779</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060473680496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157900810242</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
+    <t xml:space="preserve">0.372701585292816</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
+    <t xml:space="preserve">0.345862418413162</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082119226456</t>
+    <t xml:space="preserve">0.323082089424133</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
+    <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.357760399580002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
+    <t xml:space="preserve">0.331843703985214</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318470686674118</t>
+    <t xml:space="preserve">0.322620868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31847071647644</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32354336977005</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323543339967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
+    <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071497917175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440450668335</t>
+    <t xml:space="preserve">0.354071468114853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440480470657</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
+    <t xml:space="preserve">0.372609376907349</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609641015529633</t>
+    <t xml:space="preserve">0.616097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179735183716</t>
+    <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -69858,7 +69858,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.6911574074</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>464209</v>
@@ -69879,6 +69879,32 @@
         <v>1070</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6911689815</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>243504</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="1078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="1079">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868479013443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.368366330862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -86,46 +86,46 @@
     <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272164583206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272104978561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
+    <t xml:space="preserve">0.325196444988251</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696359395981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830327749252</t>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.2888063788414</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114499568939</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203697919846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166300058365</t>
@@ -182,49 +182,49 @@
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007667541504</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993906736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353203594684601</t>
+    <t xml:space="preserve">0.373806297779083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
     <t xml:space="preserve">0.35427314043045</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3575738966465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.357573866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344908058643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352757483720779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.344908028841019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352757513523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060473680496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157990217209</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.352318793535233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332212656736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
+    <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3246,6 +3246,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.718999981880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.684000015258789</t>
   </si>
 </sst>
 </file>
@@ -15120,7 +15123,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15146,7 +15149,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15172,7 +15175,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15198,7 +15201,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15224,7 +15227,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15250,7 +15253,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15276,7 +15279,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15302,7 +15305,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15328,7 +15331,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15354,7 +15357,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15380,7 +15383,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15406,7 +15409,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15458,7 +15461,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15484,7 +15487,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15562,7 +15565,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15588,7 +15591,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15640,7 +15643,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15666,7 +15669,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15692,7 +15695,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15744,7 +15747,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15770,7 +15773,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15796,7 +15799,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15822,7 +15825,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15848,7 +15851,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15874,7 +15877,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15952,7 +15955,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15978,7 +15981,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16030,7 +16033,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16056,7 +16059,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16082,7 +16085,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16134,7 +16137,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16160,7 +16163,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16186,7 +16189,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16212,7 +16215,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16238,7 +16241,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16290,7 +16293,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16342,7 +16345,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16394,7 +16397,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16420,7 +16423,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16550,7 +16553,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16602,7 +16605,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16628,7 +16631,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16654,7 +16657,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16680,7 +16683,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16706,7 +16709,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16732,7 +16735,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16758,7 +16761,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16784,7 +16787,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16810,7 +16813,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16836,7 +16839,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16862,7 +16865,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16992,7 +16995,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17096,7 +17099,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17122,7 +17125,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17226,7 +17229,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17252,7 +17255,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17356,7 +17359,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17382,7 +17385,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17408,7 +17411,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17434,7 +17437,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17486,7 +17489,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17512,7 +17515,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17538,7 +17541,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17564,7 +17567,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17590,7 +17593,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17616,7 +17619,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17642,7 +17645,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17668,7 +17671,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17694,7 +17697,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17720,7 +17723,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17746,7 +17749,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17772,7 +17775,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17798,7 +17801,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17824,7 +17827,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17850,7 +17853,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17876,7 +17879,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17902,7 +17905,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17928,7 +17931,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17954,7 +17957,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17980,7 +17983,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18006,7 +18009,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18032,7 +18035,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18058,7 +18061,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18084,7 +18087,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18188,7 +18191,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18266,7 +18269,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18292,7 +18295,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18318,7 +18321,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18344,7 +18347,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18370,7 +18373,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18396,7 +18399,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18422,7 +18425,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18448,7 +18451,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18474,7 +18477,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18500,7 +18503,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18526,7 +18529,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18552,7 +18555,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18578,7 +18581,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18604,7 +18607,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18630,7 +18633,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18656,7 +18659,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18682,7 +18685,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18708,7 +18711,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18734,7 +18737,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18760,7 +18763,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18786,7 +18789,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18812,7 +18815,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18838,7 +18841,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18864,7 +18867,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18890,7 +18893,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18916,7 +18919,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18942,7 +18945,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18968,7 +18971,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18994,7 +18997,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19020,7 +19023,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19046,7 +19049,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19072,7 +19075,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19098,7 +19101,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19124,7 +19127,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19150,7 +19153,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19176,7 +19179,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19202,7 +19205,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19228,7 +19231,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19254,7 +19257,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19280,7 +19283,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19306,7 +19309,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19332,7 +19335,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19358,7 +19361,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19384,7 +19387,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19410,7 +19413,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19436,7 +19439,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19462,7 +19465,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19488,7 +19491,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19514,7 +19517,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19540,7 +19543,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19566,7 +19569,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19592,7 +19595,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19618,7 +19621,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19644,7 +19647,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19670,7 +19673,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19696,7 +19699,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19722,7 +19725,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19748,7 +19751,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19774,7 +19777,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19800,7 +19803,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19826,7 +19829,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19852,7 +19855,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21620,7 +21623,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -69936,7 +69939,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6912037037</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>552712</v>
@@ -69957,6 +69960,32 @@
         <v>1057</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6912847222</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>540499</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>0.684000015258789</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676573753357</t>
+    <t xml:space="preserve">0.361676633358002</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36569008231163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196444988251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330191254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.325196385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330191224813461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.302720308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382904767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820670604706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.382904708385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.357306241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -69965,7 +69965,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6912847222</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>540499</v>
@@ -69986,6 +69986,32 @@
         <v>1078</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6909837963</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>680749</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>0.686999976634979</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36569008231163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36836639046669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012828111649</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661165475845</t>
+    <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671576023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014920473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.330191254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671605825424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014950275421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">0.294424742460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335573911667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304146736860275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.304146766662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
+    <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
+    <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
+    <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -70014,7 +70014,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6910532407</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>410883</v>
@@ -70035,6 +70035,32 @@
         <v>1073</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6911805556</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>170978</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.376928627490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868508815765</t>
+    <t xml:space="preserve">0.365868538618088</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3211829662323</t>
+    <t xml:space="preserve">0.335899710655212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
     <t xml:space="preserve">0.316634178161621</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424742460251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.294424772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471352577209</t>
+    <t xml:space="preserve">0.302720278501511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471382379532</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229546546936</t>
+    <t xml:space="preserve">0.313512802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993906736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
+    <t xml:space="preserve">0.382993936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
+    <t xml:space="preserve">0.383350759744644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806297779083</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.35427314043045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376801013947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351419389247894</t>
+    <t xml:space="preserve">0.358376771211624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060473680496</t>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70069,7 +70069,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6912268518</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>389123</v>
@@ -70090,6 +70090,32 @@
         <v>1051</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.6911458333</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>389944</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>0.685999989509583</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>0.689000010490417</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301051616669</t>
+    <t xml:space="preserve">0.365868479013443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450531482697</t>
+    <t xml:space="preserve">0.325999289751053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272164583206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450561285019</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205820083618</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -140,103 +140,103 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749387979507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512802124023</t>
+    <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.335007607936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350729942322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.354273170232773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.379157900810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.372701585292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082119226456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.317455977201462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
+    <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.323543339967728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328246980905533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328247010707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
+    <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.5856614112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,34 +1406,37 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15123,7 +15123,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15357,7 +15357,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15461,7 +15461,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15643,7 +15643,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15825,7 +15825,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15851,7 +15851,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16033,7 +16033,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16241,7 +16241,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16397,7 +16397,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16423,7 +16423,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16813,7 +16813,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16839,7 +16839,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16865,7 +16865,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16995,7 +16995,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17099,7 +17099,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17125,7 +17125,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17229,7 +17229,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17255,7 +17255,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17385,7 +17385,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18035,7 +18035,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18061,7 +18061,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18087,7 +18087,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19803,7 +19803,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19829,7 +19829,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19855,7 +19855,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21623,7 +21623,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70095,7 +70095,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6911458333</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>389944</v>
@@ -70116,6 +70116,32 @@
         <v>1046</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6912847222</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>425475</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>0.685999989509583</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>0.685999989509583</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>0.691999971866608</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -50,31 +50,31 @@
     <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.367920309305191</t>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868479013443</t>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">0.330012828111649</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272164583206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.321272104978561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191254615784</t>
+    <t xml:space="preserve">0.330191224813461</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671605825424</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696359395981</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979614973068</t>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979644775391</t>
   </si>
   <si>
     <t xml:space="preserve">0.28283029794693</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.290857315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
+    <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
     <t xml:space="preserve">0.294335544109344</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
+    <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311654806137</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.301471352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822822570801</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736692428589</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370149672031403</t>
+    <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350729942322</t>
+    <t xml:space="preserve">0.377820700407028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273170232773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.35427314043045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178721904755</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
+    <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157900810242</t>
+    <t xml:space="preserve">0.379157990217209</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
+    <t xml:space="preserve">0.3689204454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
     <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
+    <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633890628815</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341619998216629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326309829950333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
+    <t xml:space="preserve">0.319761216640472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
   </si>
   <si>
     <t xml:space="preserve">0.309892654418945</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
   </si>
   <si>
     <t xml:space="preserve">0.338300049304962</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,49 +683,49 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
+    <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531818389893</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.430714666843414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
+    <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
     <t xml:space="preserve">0.542774081230164</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
   </si>
   <si>
     <t xml:space="preserve">0.596267998218536</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
+    <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
     <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
+    <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
     <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622553706169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.622553646564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942273616791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.607796967029572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15123,7 +15123,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15149,7 +15149,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15175,7 +15175,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15201,7 +15201,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15227,7 +15227,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15253,7 +15253,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15279,7 +15279,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15305,7 +15305,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15331,7 +15331,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15357,7 +15357,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15383,7 +15383,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15409,7 +15409,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15461,7 +15461,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15487,7 +15487,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15565,7 +15565,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15591,7 +15591,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15643,7 +15643,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15669,7 +15669,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15695,7 +15695,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15747,7 +15747,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15773,7 +15773,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15799,7 +15799,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15825,7 +15825,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15851,7 +15851,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15877,7 +15877,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15955,7 +15955,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15981,7 +15981,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16033,7 +16033,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16059,7 +16059,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16085,7 +16085,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16137,7 +16137,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16163,7 +16163,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16189,7 +16189,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16215,7 +16215,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16241,7 +16241,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16293,7 +16293,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16345,7 +16345,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16397,7 +16397,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16423,7 +16423,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16553,7 +16553,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16605,7 +16605,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16631,7 +16631,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16657,7 +16657,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16683,7 +16683,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16709,7 +16709,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16735,7 +16735,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16761,7 +16761,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16787,7 +16787,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16813,7 +16813,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16839,7 +16839,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16865,7 +16865,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16995,7 +16995,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17099,7 +17099,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17125,7 +17125,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17229,7 +17229,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17255,7 +17255,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17359,7 +17359,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17385,7 +17385,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17411,7 +17411,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17437,7 +17437,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17489,7 +17489,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17515,7 +17515,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17541,7 +17541,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17567,7 +17567,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17593,7 +17593,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17619,7 +17619,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17645,7 +17645,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17671,7 +17671,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17697,7 +17697,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17723,7 +17723,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17749,7 +17749,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17775,7 +17775,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17801,7 +17801,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17827,7 +17827,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17853,7 +17853,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17879,7 +17879,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17905,7 +17905,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17931,7 +17931,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17957,7 +17957,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17983,7 +17983,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18009,7 +18009,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18035,7 +18035,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18061,7 +18061,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18087,7 +18087,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18191,7 +18191,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18269,7 +18269,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18295,7 +18295,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18321,7 +18321,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18347,7 +18347,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18373,7 +18373,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18399,7 +18399,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18425,7 +18425,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18451,7 +18451,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18477,7 +18477,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18503,7 +18503,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18529,7 +18529,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18555,7 +18555,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18581,7 +18581,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18607,7 +18607,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18633,7 +18633,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18659,7 +18659,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18685,7 +18685,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18711,7 +18711,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18737,7 +18737,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18763,7 +18763,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18789,7 +18789,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18815,7 +18815,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18841,7 +18841,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18867,7 +18867,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18893,7 +18893,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18919,7 +18919,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18945,7 +18945,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18971,7 +18971,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18997,7 +18997,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19023,7 +19023,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19049,7 +19049,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19075,7 +19075,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19101,7 +19101,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19127,7 +19127,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19153,7 +19153,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19179,7 +19179,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19205,7 +19205,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19231,7 +19231,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19257,7 +19257,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19283,7 +19283,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19309,7 +19309,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19335,7 +19335,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19361,7 +19361,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19387,7 +19387,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19413,7 +19413,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19439,7 +19439,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19465,7 +19465,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19491,7 +19491,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19517,7 +19517,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19543,7 +19543,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19569,7 +19569,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19595,7 +19595,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19621,7 +19621,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19647,7 +19647,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19673,7 +19673,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19699,7 +19699,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19725,7 +19725,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19751,7 +19751,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19777,7 +19777,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19803,7 +19803,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19829,7 +19829,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19855,7 +19855,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21623,7 +21623,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70121,7 +70121,7 @@
     </row>
     <row r="2560">
       <c r="A2560" s="1" t="n">
-        <v>46050.6912847222</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B2560" t="n">
         <v>425475</v>
@@ -70142,6 +70142,32 @@
         <v>1056</v>
       </c>
       <c r="H2560" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" s="1" t="n">
+        <v>46051.6911226852</v>
+      </c>
+      <c r="B2561" t="n">
+        <v>723339</v>
+      </c>
+      <c r="C2561" t="n">
+        <v>0.712000012397766</v>
+      </c>
+      <c r="D2561" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="E2561" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2561" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G2561" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2561" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366360664368</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366330862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330012828111649</t>
+    <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
     <t xml:space="preserve">0.321272104978561</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330191224813461</t>
+    <t xml:space="preserve">0.325196444988251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
     <t xml:space="preserve">0.314671605825424</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696359395981</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979644775391</t>
+    <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
     <t xml:space="preserve">0.28283029794693</t>
@@ -137,22 +137,22 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471352577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.301471322774887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">0.328229546546936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
+    <t xml:space="preserve">0.335007667541504</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820700407028</t>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350789546967</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
@@ -70147,7 +70147,7 @@
     </row>
     <row r="2561">
       <c r="A2561" s="1" t="n">
-        <v>46051.6911226852</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2561" t="n">
         <v>723339</v>
@@ -70168,6 +70168,32 @@
         <v>1049</v>
       </c>
       <c r="H2561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="1" t="n">
+        <v>46052.6243402778</v>
+      </c>
+      <c r="B2562" t="n">
+        <v>84564</v>
+      </c>
+      <c r="C2562" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="D2562" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="E2562" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H2562" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36569008231163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36836639046669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012828111649</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661165475845</t>
+    <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.330191224813461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671576023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014920473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.330191254615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671605825424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014950275421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">0.294424742460251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.290857285261154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335573911667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304146736860275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.304146766662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
+    <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869625329971</t>
+    <t xml:space="preserve">0.313869595527649</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
+    <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
+    <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183942079544</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
+    <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -70199,7 +70199,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.691087963</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>229439</v>
@@ -70220,6 +70220,32 @@
         <v>1078</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6912962963</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>442365</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.37692865729332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321182936429977</t>
+    <t xml:space="preserve">0.33589968085289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3211829662323</t>
   </si>
   <si>
     <t xml:space="preserve">0.316634178161621</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.294424742460251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
+    <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335514307022</t>
+    <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229516744614</t>
+    <t xml:space="preserve">0.313512772321701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229546546936</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
+    <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
+    <t xml:space="preserve">0.383350789546967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806297779083</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.354273110628128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351419359445572</t>
+    <t xml:space="preserve">0.358376801013947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351419389247894</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060473680496</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
+    <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805345058441</t>
+    <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.349367827177048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
+    <t xml:space="preserve">0.354163706302643</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.341712236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
+    <t xml:space="preserve">0.322620838880539</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
+    <t xml:space="preserve">0.312660068273544</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333532810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328246980905533</t>
+    <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.32621756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
+    <t xml:space="preserve">0.37565353512764</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517108917236</t>
+    <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
+    <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
+    <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465383529663</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70254,7 +70254,7 @@
     </row>
     <row r="2565">
       <c r="A2565" s="1" t="n">
-        <v>46057.6913078704</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2565" t="n">
         <v>497055</v>
@@ -70275,6 +70275,32 @@
         <v>1048</v>
       </c>
       <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.6911805556</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>395036</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>0.704999983310699</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>0.693000018596649</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H2566" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
+    <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984754085541</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868508815765</t>
+    <t xml:space="preserve">0.368366330862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868538618088</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
@@ -65,22 +65,22 @@
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36569008231163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3211829662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316634178161621</t>
+    <t xml:space="preserve">0.335899710655212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321182936429977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316634207963943</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999319553375</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661195278168</t>
+    <t xml:space="preserve">0.324661165475845</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014920473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.314671576023102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014890670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424742460251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.294424772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304146736860275</t>
+    <t xml:space="preserve">0.304146707057953</t>
   </si>
   <si>
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.302720278501511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229546546936</t>
+    <t xml:space="preserve">0.313512802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">0.382993906736374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370149672031403</t>
+    <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354273110628128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.35427314043045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376801013947</t>
+    <t xml:space="preserve">0.358376741409302</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579116821289</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351419389247894</t>
+    <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
     <t xml:space="preserve">0.344908028841019</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060473680496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70280,7 +70280,7 @@
     </row>
     <row r="2566">
       <c r="A2566" s="1" t="n">
-        <v>46058.6911805556</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2566" t="n">
         <v>395036</v>
@@ -70301,6 +70301,32 @@
         <v>1058</v>
       </c>
       <c r="H2566" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" s="1" t="n">
+        <v>46059.6910069444</v>
+      </c>
+      <c r="B2567" t="n">
+        <v>285945</v>
+      </c>
+      <c r="C2567" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="D2567" t="n">
+        <v>0.683000028133392</v>
+      </c>
+      <c r="E2567" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>0.689000010490417</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H2567" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868538618088</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36569008231163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634207963943</t>
+    <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999319553375</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661165475845</t>
+    <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014890670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358235120773</t>
+    <t xml:space="preserve">0.314671605825424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014920473099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304146707057953</t>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
     <t xml:space="preserve">0.30120375752449</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471352577209</t>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471382379532</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33349198102951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.333491951227188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993906736374</t>
+    <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.37014964222908</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063541889191</t>
+    <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806297779083</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.358376771211624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.39658984541893</t>
@@ -70306,7 +70306,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6910069444</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>285945</v>
@@ -70327,6 +70327,32 @@
         <v>1051</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.6909722222</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>342611</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>0.700999975204468</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301051616669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.365868508815765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301081418991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690141916275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424772262573</t>
+    <t xml:space="preserve">0.28283029794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424802064896</t>
   </si>
   <si>
     <t xml:space="preserve">0.290857285261154</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
+    <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203727722168</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560580730438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007637739182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.335007607936859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.383350729942322</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">0.352579087018967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757483720779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.352757453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306301593781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060414075851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.372701585292816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.369197130203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -374,52 +374,52 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323082119226456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.317455977201462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323082089424133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
+    <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
     <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315426558256149</t>
+    <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.318470686674118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.31847071647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32354336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.323543339967728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354440450668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.354440480470657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328246980905533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328247010707855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
+    <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.322344154119492</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
+    <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609376907349</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.380449414253235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935125112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -755,28 +755,28 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.636849105358124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.602724373340607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.5856614112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,34 +1406,37 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15126,7 +15126,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15152,7 +15152,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15178,7 +15178,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15204,7 +15204,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15230,7 +15230,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15256,7 +15256,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15282,7 +15282,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15308,7 +15308,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15334,7 +15334,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15360,7 +15360,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15386,7 +15386,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15412,7 +15412,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15464,7 +15464,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15490,7 +15490,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15568,7 +15568,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15594,7 +15594,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15646,7 +15646,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15672,7 +15672,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15698,7 +15698,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15750,7 +15750,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15776,7 +15776,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15802,7 +15802,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15828,7 +15828,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15854,7 +15854,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15880,7 +15880,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15958,7 +15958,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15984,7 +15984,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16036,7 +16036,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16062,7 +16062,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16088,7 +16088,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16140,7 +16140,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16166,7 +16166,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16192,7 +16192,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16218,7 +16218,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16244,7 +16244,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16296,7 +16296,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16348,7 +16348,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16400,7 +16400,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16426,7 +16426,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16556,7 +16556,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16608,7 +16608,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16634,7 +16634,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16660,7 +16660,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16686,7 +16686,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16712,7 +16712,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16738,7 +16738,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16764,7 +16764,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16790,7 +16790,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16816,7 +16816,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16842,7 +16842,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16868,7 +16868,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16998,7 +16998,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17102,7 +17102,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17128,7 +17128,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17232,7 +17232,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17258,7 +17258,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17362,7 +17362,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17388,7 +17388,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17414,7 +17414,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17440,7 +17440,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17492,7 +17492,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17518,7 +17518,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17544,7 +17544,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17570,7 +17570,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17596,7 +17596,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17622,7 +17622,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17648,7 +17648,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17674,7 +17674,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17700,7 +17700,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17726,7 +17726,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17752,7 +17752,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17778,7 +17778,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17804,7 +17804,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17830,7 +17830,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17882,7 +17882,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17908,7 +17908,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17934,7 +17934,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17960,7 +17960,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17986,7 +17986,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18012,7 +18012,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18038,7 +18038,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18064,7 +18064,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18090,7 +18090,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18194,7 +18194,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18272,7 +18272,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18298,7 +18298,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18324,7 +18324,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18350,7 +18350,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18376,7 +18376,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18402,7 +18402,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18428,7 +18428,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18454,7 +18454,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18480,7 +18480,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18506,7 +18506,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18532,7 +18532,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18558,7 +18558,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18584,7 +18584,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18610,7 +18610,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18636,7 +18636,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18662,7 +18662,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18688,7 +18688,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18714,7 +18714,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18740,7 +18740,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18766,7 +18766,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18792,7 +18792,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18818,7 +18818,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18844,7 +18844,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18870,7 +18870,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18896,7 +18896,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18922,7 +18922,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18948,7 +18948,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18974,7 +18974,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19000,7 +19000,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19026,7 +19026,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19052,7 +19052,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19078,7 +19078,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19104,7 +19104,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19130,7 +19130,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19156,7 +19156,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19182,7 +19182,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19208,7 +19208,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19234,7 +19234,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19260,7 +19260,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19286,7 +19286,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19312,7 +19312,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19338,7 +19338,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19364,7 +19364,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19390,7 +19390,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19416,7 +19416,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19442,7 +19442,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19468,7 +19468,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19494,7 +19494,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19520,7 +19520,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19546,7 +19546,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19572,7 +19572,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19598,7 +19598,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19624,7 +19624,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19650,7 +19650,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19676,7 +19676,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19702,7 +19702,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19728,7 +19728,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19754,7 +19754,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19780,7 +19780,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19806,7 +19806,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19832,7 +19832,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19858,7 +19858,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21626,7 +21626,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70332,7 +70332,7 @@
     </row>
     <row r="2568">
       <c r="A2568" s="1" t="n">
-        <v>46062.6909722222</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2568" t="n">
         <v>342611</v>
@@ -70353,6 +70353,32 @@
         <v>1049</v>
       </c>
       <c r="H2568" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" s="1" t="n">
+        <v>46063.6910300926</v>
+      </c>
+      <c r="B2569" t="n">
+        <v>354854</v>
+      </c>
+      <c r="C2569" t="n">
+        <v>0.705999970436096</v>
+      </c>
+      <c r="D2569" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="E2569" t="n">
+        <v>0.690999984741211</v>
+      </c>
+      <c r="F2569" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H2569" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
+    <t xml:space="preserve">0.368366330862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">0.366849809885025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690141916275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,28 +98,28 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
+    <t xml:space="preserve">0.325196444988251</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294424802064896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.294424772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560580730438</t>
+    <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
     <t xml:space="preserve">0.301471322774887</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.313512772321701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820700407028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350729942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
+    <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
     <t xml:space="preserve">0.354183971881866</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306301593781</t>
+    <t xml:space="preserve">0.352757513523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060414075851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157990217209</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
+    <t xml:space="preserve">0.3689204454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
     <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
+    <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633890628815</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341619998216629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326309829950333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
+    <t xml:space="preserve">0.319761216640472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
   </si>
   <si>
     <t xml:space="preserve">0.309892654418945</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
   </si>
   <si>
     <t xml:space="preserve">0.338300049304962</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,49 +683,49 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
+    <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531818389893</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.430714666843414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
+    <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
     <t xml:space="preserve">0.542774081230164</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
   </si>
   <si>
     <t xml:space="preserve">0.596267998218536</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
+    <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
     <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
+    <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
     <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622553706169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.622553646564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942273616791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.607796967029572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15126,7 +15126,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15152,7 +15152,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15178,7 +15178,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15204,7 +15204,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15230,7 +15230,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15256,7 +15256,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15282,7 +15282,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15308,7 +15308,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15334,7 +15334,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15360,7 +15360,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15386,7 +15386,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15412,7 +15412,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15464,7 +15464,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15490,7 +15490,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15568,7 +15568,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15594,7 +15594,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15646,7 +15646,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15672,7 +15672,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15698,7 +15698,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15750,7 +15750,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15776,7 +15776,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15802,7 +15802,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15828,7 +15828,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15854,7 +15854,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15880,7 +15880,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15958,7 +15958,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15984,7 +15984,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16036,7 +16036,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16062,7 +16062,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16088,7 +16088,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16140,7 +16140,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16166,7 +16166,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16192,7 +16192,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16218,7 +16218,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16244,7 +16244,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16296,7 +16296,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16348,7 +16348,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16400,7 +16400,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16426,7 +16426,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16556,7 +16556,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16608,7 +16608,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16634,7 +16634,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16660,7 +16660,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16686,7 +16686,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16712,7 +16712,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16738,7 +16738,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16764,7 +16764,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16790,7 +16790,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16816,7 +16816,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16842,7 +16842,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16868,7 +16868,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16998,7 +16998,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17102,7 +17102,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17128,7 +17128,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17232,7 +17232,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17258,7 +17258,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17362,7 +17362,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17388,7 +17388,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17414,7 +17414,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17440,7 +17440,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17492,7 +17492,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17518,7 +17518,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17544,7 +17544,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17570,7 +17570,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17596,7 +17596,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17622,7 +17622,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17648,7 +17648,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17674,7 +17674,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17700,7 +17700,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17726,7 +17726,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17752,7 +17752,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17778,7 +17778,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17804,7 +17804,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17830,7 +17830,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17882,7 +17882,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17908,7 +17908,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17934,7 +17934,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17960,7 +17960,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17986,7 +17986,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18012,7 +18012,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18038,7 +18038,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18064,7 +18064,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18090,7 +18090,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18194,7 +18194,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18272,7 +18272,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18298,7 +18298,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18324,7 +18324,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18350,7 +18350,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18376,7 +18376,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18402,7 +18402,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18428,7 +18428,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18454,7 +18454,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18480,7 +18480,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18506,7 +18506,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18532,7 +18532,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18558,7 +18558,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18584,7 +18584,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18610,7 +18610,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18636,7 +18636,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18662,7 +18662,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18688,7 +18688,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18714,7 +18714,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18740,7 +18740,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18766,7 +18766,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18792,7 +18792,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18818,7 +18818,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18844,7 +18844,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18870,7 +18870,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18896,7 +18896,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18922,7 +18922,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18948,7 +18948,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18974,7 +18974,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19000,7 +19000,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19026,7 +19026,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19052,7 +19052,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19078,7 +19078,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19104,7 +19104,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19130,7 +19130,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19156,7 +19156,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19182,7 +19182,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19208,7 +19208,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19234,7 +19234,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19260,7 +19260,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19286,7 +19286,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19312,7 +19312,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19338,7 +19338,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19364,7 +19364,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19390,7 +19390,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19416,7 +19416,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19442,7 +19442,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19468,7 +19468,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19494,7 +19494,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19520,7 +19520,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19546,7 +19546,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19572,7 +19572,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19598,7 +19598,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19624,7 +19624,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19650,7 +19650,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19676,7 +19676,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19702,7 +19702,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19728,7 +19728,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19754,7 +19754,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19780,7 +19780,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19806,7 +19806,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19832,7 +19832,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19858,7 +19858,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21626,7 +21626,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70358,7 +70358,7 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46063.6910300926</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2569" t="n">
         <v>354854</v>
@@ -70379,6 +70379,32 @@
         <v>1073</v>
       </c>
       <c r="H2569" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="1" t="n">
+        <v>46064.6910069444</v>
+      </c>
+      <c r="B2570" t="n">
+        <v>343815</v>
+      </c>
+      <c r="C2570" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="D2570" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="E2570" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="F2570" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H2570" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676573753357</t>
+    <t xml:space="preserve">0.361676633358002</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920309305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366330862045</t>
+    <t xml:space="preserve">0.373984754085541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.36569008231163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196444988251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330191254615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.325196385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330191224813461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673668384552</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
+    <t xml:space="preserve">0.302720308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
+    <t xml:space="preserve">0.372736692428589</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382904767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820670604706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350789546967</t>
+    <t xml:space="preserve">0.382904708385468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820730209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">0.352757513523102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.357306241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70384,7 +70384,7 @@
     </row>
     <row r="2570">
       <c r="A2570" s="1" t="n">
-        <v>46064.6910069444</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B2570" t="n">
         <v>343815</v>
@@ -70405,6 +70405,32 @@
         <v>1072</v>
       </c>
       <c r="H2570" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" s="1" t="n">
+        <v>46065.6912268518</v>
+      </c>
+      <c r="B2571" t="n">
+        <v>409942</v>
+      </c>
+      <c r="C2571" t="n">
+        <v>0.708999991416931</v>
+      </c>
+      <c r="D2571" t="n">
+        <v>0.699000000953674</v>
+      </c>
+      <c r="E2571" t="n">
+        <v>0.703000009059906</v>
+      </c>
+      <c r="F2571" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="G2571" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H2571" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="1081">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920368909836</t>
+    <t xml:space="preserve">0.376928627490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920339107513</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.335899740457535</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
+    <t xml:space="preserve">0.325999289751053</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012828111649</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321450531482697</t>
+    <t xml:space="preserve">0.321450561285019</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -104,28 +104,28 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014920473099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.314671605825424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014950275421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28283029794693</t>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
   </si>
   <si>
     <t xml:space="preserve">0.288806408643723</t>
@@ -137,52 +137,52 @@
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335573911667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">0.335007607936859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333491951227188</t>
+    <t xml:space="preserve">0.33349198102951</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.370149672031403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820730209351</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063512086868</t>
+    <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806327581406</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">0.353203564882278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.354273170232773</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573926448822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.3575738966465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
+    <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579116821289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465969562531</t>
+    <t xml:space="preserve">0.352757453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465999364853</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370060443878174</t>
+    <t xml:space="preserve">0.370060414075851</t>
   </si>
   <si>
     <t xml:space="preserve">0.379157930612564</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701615095139</t>
+    <t xml:space="preserve">0.372701585292816</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368828147649765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925320863724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359697580337524</t>
+    <t xml:space="preserve">0.368828177452087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925291061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
     <t xml:space="preserve">0.356468945741653</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
+    <t xml:space="preserve">0.345862418413162</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.341251015663147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082119226456</t>
+    <t xml:space="preserve">0.323082089424133</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329169452190399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345033138990402</t>
+    <t xml:space="preserve">0.329169481992722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34503310918808</t>
   </si>
   <si>
     <t xml:space="preserve">0.349367797374725</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
+    <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341619998216629</t>
+    <t xml:space="preserve">0.357760399580002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341620028018951</t>
   </si>
   <si>
     <t xml:space="preserve">0.341712266206741</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
+    <t xml:space="preserve">0.331843703985214</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,25 +485,25 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426528453827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.318470686674118</t>
+    <t xml:space="preserve">0.322620868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31847071647644</t>
   </si>
   <si>
     <t xml:space="preserve">0.320960432291031</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761216640472</t>
+    <t xml:space="preserve">0.319761246442795</t>
   </si>
   <si>
     <t xml:space="preserve">0.312660098075867</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">0.31182986497879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32354336977005</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323543339967728</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
+    <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">0.340605288743973</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071497917175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440450668335</t>
+    <t xml:space="preserve">0.354071468114853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440480470657</t>
   </si>
   <si>
     <t xml:space="preserve">0.356837928295135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
+    <t xml:space="preserve">0.353333473205566</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.325387358665466</t>
+    <t xml:space="preserve">0.322897642850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.325387388467789</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110614299774</t>
+    <t xml:space="preserve">0.325110644102097</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595508098602</t>
+    <t xml:space="preserve">0.352595537900925</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">0.385429799556732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
+    <t xml:space="preserve">0.372609376907349</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379342466592789</t>
+    <t xml:space="preserve">0.379342436790466</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433388859033585</t>
+    <t xml:space="preserve">0.433388888835907</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48881995677948</t>
+    <t xml:space="preserve">0.488819897174835</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846734523773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.547846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">0.599495708942413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
+    <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
     <t xml:space="preserve">0.640999317169189</t>
@@ -899,22 +899,22 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609641015529633</t>
+    <t xml:space="preserve">0.616097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
     <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
+    <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617942273616791</t>
+    <t xml:space="preserve">0.617942214012146</t>
   </si>
   <si>
     <t xml:space="preserve">0.618863821029663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607796967029572</t>
+    <t xml:space="preserve">0.607797026634216</t>
   </si>
   <si>
     <t xml:space="preserve">0.617480993270874</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179735183716</t>
+    <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
     <t xml:space="preserve">0.612408339977264</t>
@@ -3252,6 +3252,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.695999979972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.726000010967255</t>
   </si>
 </sst>
 </file>
@@ -70462,7 +70465,7 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46069.6910532407</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B2573" t="n">
         <v>929905</v>
@@ -70483,6 +70486,32 @@
         <v>1047</v>
       </c>
       <c r="H2573" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" s="1" t="n">
+        <v>46070.6912962963</v>
+      </c>
+      <c r="B2574" t="n">
+        <v>467181</v>
+      </c>
+      <c r="C2574" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="D2574" t="n">
+        <v>0.703999996185303</v>
+      </c>
+      <c r="E2574" t="n">
+        <v>0.708000004291534</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>0.726000010967255</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H2574" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="1084">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920339107513</t>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
     <t xml:space="preserve">0.368366360664368</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673668384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.288984835147858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673698186874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29174941778183</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114529371262</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289876013994217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290054440498352</t>
+    <t xml:space="preserve">0.289875984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29005441069603</t>
   </si>
   <si>
     <t xml:space="preserve">0.290500462055206</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -191,25 +191,25 @@
     <t xml:space="preserve">0.328229516744614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335007607936859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33349198102951</t>
+    <t xml:space="preserve">0.335007637739182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.370149672031403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
+    <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579087018967</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465999364853</t>
+    <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
     <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357306301593781</t>
+    <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
     <t xml:space="preserve">0.362122625112534</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.372332632541656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372701585292816</t>
+    <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
     <t xml:space="preserve">0.370027363300323</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368828177452087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362925291061401</t>
+    <t xml:space="preserve">0.3689204454422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368828147649765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
     <t xml:space="preserve">0.359697610139847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
+    <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633890628815</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
+    <t xml:space="preserve">0.341251045465469</t>
   </si>
   <si>
     <t xml:space="preserve">0.32372784614563</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323082089424133</t>
+    <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329169481992722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34503310918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.329169452190399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345033138990402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341620028018951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341619998216629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.326402068138123</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326309829950333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31847071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620838880539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318470686674118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">0.318562924861908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319761246442795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
+    <t xml:space="preserve">0.319761216640472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
   </si>
   <si>
     <t xml:space="preserve">0.309892654418945</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323543339967728</t>
+    <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
     <t xml:space="preserve">0.324189066886902</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">0.338484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354440480470657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354440450668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
   </si>
   <si>
     <t xml:space="preserve">0.338300049304962</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325387388467789</t>
+    <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
     <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325110644102097</t>
+    <t xml:space="preserve">0.325110614299774</t>
   </si>
   <si>
     <t xml:space="preserve">0.328062504529953</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">0.32621756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.355086177587509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352595537900925</t>
+    <t xml:space="preserve">0.352595508098602</t>
   </si>
   <si>
     <t xml:space="preserve">0.347984105348587</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,49 +683,49 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379342436790466</t>
+    <t xml:space="preserve">0.380449384450912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379342466592789</t>
   </si>
   <si>
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
+    <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531818389893</t>
@@ -752,16 +752,16 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.433388888835907</t>
+    <t xml:space="preserve">0.430714666843414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.433388859033585</t>
   </si>
   <si>
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">0.48374730348587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488819897174835</t>
+    <t xml:space="preserve">0.48881995677948</t>
   </si>
   <si>
     <t xml:space="preserve">0.507265567779541</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547846794128418</t>
+    <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
     <t xml:space="preserve">0.542774081230164</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
   </si>
   <si>
     <t xml:space="preserve">0.596267998218536</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
+    <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
     <t xml:space="preserve">0.634542942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602724373340607</t>
+    <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
     <t xml:space="preserve">0.62808758020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622553706169128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617942214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.622553646564484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617942273616791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -932,37 +932,37 @@
     <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607797026634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.607796967029572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1436,9 +1439,6 @@
     <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.455594688653946</t>
   </si>
   <si>
@@ -3261,6 +3261,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.727999985218048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.737999975681305</t>
   </si>
 </sst>
 </file>
@@ -15135,7 +15138,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15161,7 +15164,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15187,7 +15190,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15213,7 +15216,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15239,7 +15242,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15265,7 +15268,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15291,7 +15294,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15317,7 +15320,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15343,7 +15346,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15369,7 +15372,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15395,7 +15398,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15421,7 +15424,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15473,7 +15476,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15499,7 +15502,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15577,7 +15580,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15603,7 +15606,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15655,7 +15658,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15681,7 +15684,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15707,7 +15710,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15759,7 +15762,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15785,7 +15788,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15811,7 +15814,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15837,7 +15840,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15863,7 +15866,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15889,7 +15892,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15967,7 +15970,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15993,7 +15996,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16045,7 +16048,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16071,7 +16074,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16097,7 +16100,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16149,7 +16152,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16175,7 +16178,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16201,7 +16204,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16227,7 +16230,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16253,7 +16256,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16305,7 +16308,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16357,7 +16360,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16409,7 +16412,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16435,7 +16438,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16565,7 +16568,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16617,7 +16620,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16643,7 +16646,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16669,7 +16672,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16695,7 +16698,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16721,7 +16724,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16747,7 +16750,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16773,7 +16776,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16799,7 +16802,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16825,7 +16828,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16851,7 +16854,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16877,7 +16880,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17007,7 +17010,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17111,7 +17114,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17137,7 +17140,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17241,7 +17244,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17267,7 +17270,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17371,7 +17374,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17397,7 +17400,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17423,7 +17426,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17449,7 +17452,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17501,7 +17504,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17527,7 +17530,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17553,7 +17556,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17579,7 +17582,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17605,7 +17608,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17631,7 +17634,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17657,7 +17660,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17683,7 +17686,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17709,7 +17712,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17735,7 +17738,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17761,7 +17764,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17787,7 +17790,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17813,7 +17816,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17839,7 +17842,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17865,7 +17868,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17891,7 +17894,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17917,7 +17920,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17943,7 +17946,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17969,7 +17972,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17995,7 +17998,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18021,7 +18024,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18047,7 +18050,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18073,7 +18076,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18099,7 +18102,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18203,7 +18206,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18281,7 +18284,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18307,7 +18310,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18333,7 +18336,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18359,7 +18362,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18385,7 +18388,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18411,7 +18414,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18437,7 +18440,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18463,7 +18466,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18489,7 +18492,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18515,7 +18518,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18541,7 +18544,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18567,7 +18570,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18593,7 +18596,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18619,7 +18622,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18645,7 +18648,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18671,7 +18674,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18697,7 +18700,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18723,7 +18726,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18749,7 +18752,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18775,7 +18778,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18801,7 +18804,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18827,7 +18830,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18853,7 +18856,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18879,7 +18882,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18905,7 +18908,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18931,7 +18934,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18957,7 +18960,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18983,7 +18986,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19009,7 +19012,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19035,7 +19038,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19061,7 +19064,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19087,7 +19090,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19113,7 +19116,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19139,7 +19142,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19165,7 +19168,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19191,7 +19194,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19217,7 +19220,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19243,7 +19246,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19269,7 +19272,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19295,7 +19298,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19321,7 +19324,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19347,7 +19350,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19373,7 +19376,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19399,7 +19402,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19425,7 +19428,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19451,7 +19454,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19477,7 +19480,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19503,7 +19506,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19529,7 +19532,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19555,7 +19558,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19581,7 +19584,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19607,7 +19610,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19633,7 +19636,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19659,7 +19662,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19685,7 +19688,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19711,7 +19714,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19737,7 +19740,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19763,7 +19766,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19789,7 +19792,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19815,7 +19818,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19841,7 +19844,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19867,7 +19870,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21635,7 +21638,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70549,7 +70552,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.6910763889</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>480462</v>
@@ -70570,6 +70573,32 @@
         <v>1082</v>
       </c>
       <c r="H2576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.6912731481</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>370871</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>0.726999998092651</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>0.737999975681305</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H2577" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
+    <t xml:space="preserve">0.365868479013443</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301051616669</t>
+    <t xml:space="preserve">0.362301081418991</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012857913971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450531482697</t>
+    <t xml:space="preserve">0.325999289751053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012828111649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272164583206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450561285019</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
+    <t xml:space="preserve">0.314671576023102</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">0.307358264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">0.308696389198303</t>
+    <t xml:space="preserve">0.308696359395981</t>
   </si>
   <si>
     <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205820083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.293979614973068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830268144608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.282205849885941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.293979585170746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830327749252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749387979507</t>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749358177185</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114499568939</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.294335514307022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.289875984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
+    <t xml:space="preserve">0.289876013994217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500491857529</t>
   </si>
   <si>
     <t xml:space="preserve">0.300311625003815</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.30120375752449</t>
+    <t xml:space="preserve">0.301203697919846</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.303166329860687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869625329971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313512802124023</t>
+    <t xml:space="preserve">0.303166300058365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471322774887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869595527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
@@ -200,31 +200,31 @@
     <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372736722230911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37014964222908</t>
+    <t xml:space="preserve">0.372736692428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370149672031403</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820700407028</t>
+    <t xml:space="preserve">0.377820730209351</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353203564882278</t>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353203594684601</t>
   </si>
   <si>
     <t xml:space="preserve">0.35427314043045</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178751707077</t>
+    <t xml:space="preserve">0.359178721904755</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -254,31 +254,31 @@
     <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344908028841019</t>
+    <t xml:space="preserve">0.344908058643341</t>
   </si>
   <si>
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465969562531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.358465999364853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060443878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.362122625112534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060473680496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157930612564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027393102646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37150239944458</t>
+    <t xml:space="preserve">0.370027363300323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371502429246902</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
+    <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -332,40 +332,40 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197160005569</t>
+    <t xml:space="preserve">0.369197130203247</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.364309012889862</t>
+    <t xml:space="preserve">0.36430898308754</t>
   </si>
   <si>
     <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356007754802704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251045465469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32372784614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.356007725000381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251015663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.323727816343307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.337838798761368</t>
+    <t xml:space="preserve">0.33783882856369</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
+    <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805345058441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582539558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567830085754</t>
+    <t xml:space="preserve">0.322805374860764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582569360733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567800283432</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935071706772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886932134628</t>
+    <t xml:space="preserve">0.350935101509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886961936951</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352318793535233</t>
+    <t xml:space="preserve">0.35231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344756424427032</t>
+    <t xml:space="preserve">0.34475639462471</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760399580002</t>
+    <t xml:space="preserve">0.357760369777679</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
+    <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028180360794</t>
+    <t xml:space="preserve">0.332028150558472</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
@@ -482,34 +482,34 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316349029541016</t>
+    <t xml:space="preserve">0.315611034631729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316348999738693</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426558256149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620868682861</t>
+    <t xml:space="preserve">0.326402097940445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32630980014801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426528453827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620838880539</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960402488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518796443939</t>
+    <t xml:space="preserve">0.320960432291031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518826246262</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305795192719</t>
+    <t xml:space="preserve">0.313305824995041</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
@@ -548,46 +548,46 @@
     <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722887516022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907393693924</t>
+    <t xml:space="preserve">0.310722917318344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907363891602</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189096689224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605318546295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833923339844</t>
+    <t xml:space="preserve">0.324189066886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338484555482864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605288743973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833953142166</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071468114853</t>
+    <t xml:space="preserve">0.354071497917175</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333532810211</t>
+    <t xml:space="preserve">0.356837928295135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.33830001950264</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32612532377243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324004590511322</t>
+    <t xml:space="preserve">0.326125353574753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
     <t xml:space="preserve">0.322897613048553</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328246980905533</t>
+    <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558079242706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326217591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.324558049440384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32621756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397162914276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.332397192716599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241235017776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.353241264820099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396322250366</t>
+    <t xml:space="preserve">0.351396292448044</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429829359055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609376907349</t>
+    <t xml:space="preserve">0.385429799556732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449384450912</t>
+    <t xml:space="preserve">0.380449414253235</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37860444188118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162835836411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37574577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.381370931863785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.378604471683502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517138719559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162865638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.375745743513107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935154914856</t>
+    <t xml:space="preserve">0.369935125112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531848192215</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757871389389</t>
+    <t xml:space="preserve">0.433757841587067</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286023139954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105545520782</t>
+    <t xml:space="preserve">0.475446045398712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839428663254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286052942276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105605125427</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245112419128</t>
+    <t xml:space="preserve">0.531245172023773</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557992041110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225551128387</t>
+    <t xml:space="preserve">0.557991981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225610733032</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610102236270905</t>
+    <t xml:space="preserve">0.61010217666626</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849164962769</t>
+    <t xml:space="preserve">0.636849105358124</t>
   </si>
   <si>
     <t xml:space="preserve">0.634543001651764</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844200134277</t>
+    <t xml:space="preserve">0.648378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844259738922</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609640955924988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724313735962</t>
+    <t xml:space="preserve">0.616097271442413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609641015529633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724373340607</t>
   </si>
   <si>
     <t xml:space="preserve">0.628087520599365</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
+    <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165079116821</t>
+    <t xml:space="preserve">0.635465443134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165138721466</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179794788361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408399581909</t>
+    <t xml:space="preserve">0.609179735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408339977264</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829319477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.613070249557495</t>
+    <t xml:space="preserve">0.608829379081726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61307030916214</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969141960144</t>
+    <t xml:space="preserve">0.581969201564789</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573958694934845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152659893036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555200576782</t>
+    <t xml:space="preserve">0.57395875453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555260181427</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627104282379</t>
+    <t xml:space="preserve">0.546627163887024</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.5339035987854</t>
+    <t xml:space="preserve">0.547569811344147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.533903539180756</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432185649872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741928577423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396800041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972292423248</t>
+    <t xml:space="preserve">0.533432245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396740436554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972352027893</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539086997509003</t>
+    <t xml:space="preserve">0.539087057113647</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580258369446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349834918976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731362342834</t>
+    <t xml:space="preserve">0.555108964443207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580198764801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349894523621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040091991425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731421947479</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454033374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54238623380661</t>
+    <t xml:space="preserve">0.538615763187408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454092979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.542386293411255</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777314186096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.524479150772095</t>
+    <t xml:space="preserve">0.527777373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52447909116745</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065209388733</t>
+    <t xml:space="preserve">0.523065149784088</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180868148804</t>
+    <t xml:space="preserve">0.521180927753448</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720080852509</t>
+    <t xml:space="preserve">0.528720021247864</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292422771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994199752808</t>
+    <t xml:space="preserve">0.560292482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994140148163</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,28 +1148,25 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603645801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.592807471752167</t>
+    <t xml:space="preserve">0.592807531356812</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577107906342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59516316652298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772086143494</t>
+    <t xml:space="preserve">0.596577048301697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.595163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772026538849</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876284599304</t>
+    <t xml:space="preserve">0.599876224994659</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1187,10 +1184,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670918941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947234630585</t>
+    <t xml:space="preserve">0.578670859336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947294235229</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533293247223</t>
+    <t xml:space="preserve">0.564533352851868</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1217,7 +1214,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537673115730286</t>
+    <t xml:space="preserve">0.53767317533493</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1232,7 +1229,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100654602051</t>
+    <t xml:space="preserve">0.506100714206696</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5437992811203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194495439529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49290668964386</t>
+    <t xml:space="preserve">0.543799221515656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997350215912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194525241852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.492906719446182</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1271,7 +1268,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512226819992065</t>
+    <t xml:space="preserve">0.51222687959671</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684516429901</t>
+    <t xml:space="preserve">0.545684456825256</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1295,19 +1292,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51835298538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49384930729866</t>
+    <t xml:space="preserve">0.518352925777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.493849337100983</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078777074814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539653778076</t>
+    <t xml:space="preserve">0.490078747272491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539623975754</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1316,7 +1313,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770047426224</t>
+    <t xml:space="preserve">0.478770077228546</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1325,13 +1322,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251818180084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021364927292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.489137142896652</t>
+    <t xml:space="preserve">0.487251847982407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021424531937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48913711309433</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1349,7 +1346,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931687831879</t>
+    <t xml:space="preserve">0.467931717634201</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1382,7 +1379,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909810304642</t>
+    <t xml:space="preserve">0.451909840106964</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1400,7 +1397,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469815999269485</t>
+    <t xml:space="preserve">0.469816029071808</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1409,34 +1406,37 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517776250839</t>
+    <t xml:space="preserve">0.466517746448517</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977669477463</t>
+    <t xml:space="preserve">0.458977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458036005496979</t>
+    <t xml:space="preserve">0.458035975694656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506375551224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463689863681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.473547101020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46238762140274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.458506345748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463689863681793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.473547101020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46238762140274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.463843464851379</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15141,7 +15141,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>378</v>
+        <v>314</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15167,7 +15167,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15193,7 +15193,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15219,7 +15219,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15245,7 +15245,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15271,7 +15271,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15297,7 +15297,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15323,7 +15323,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15349,7 +15349,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15375,7 +15375,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15401,7 +15401,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15427,7 +15427,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15479,7 +15479,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15505,7 +15505,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15583,7 +15583,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15609,7 +15609,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15661,7 +15661,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15687,7 +15687,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15713,7 +15713,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15765,7 +15765,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15791,7 +15791,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15817,7 +15817,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15843,7 +15843,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15869,7 +15869,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15895,7 +15895,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15973,7 +15973,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15999,7 +15999,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16051,7 +16051,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16077,7 +16077,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16103,7 +16103,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16155,7 +16155,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16181,7 +16181,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16207,7 +16207,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16233,7 +16233,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16259,7 +16259,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16311,7 +16311,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16363,7 +16363,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16415,7 +16415,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16441,7 +16441,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16571,7 +16571,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16623,7 +16623,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16649,7 +16649,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16675,7 +16675,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16701,7 +16701,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16727,7 +16727,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16753,7 +16753,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16779,7 +16779,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16805,7 +16805,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16831,7 +16831,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16857,7 +16857,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16883,7 +16883,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17013,7 +17013,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17117,7 +17117,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17143,7 +17143,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17247,7 +17247,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17273,7 +17273,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17377,7 +17377,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17403,7 +17403,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17429,7 +17429,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17455,7 +17455,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17507,7 +17507,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17533,7 +17533,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17559,7 +17559,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17585,7 +17585,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17611,7 +17611,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17637,7 +17637,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17663,7 +17663,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17689,7 +17689,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17715,7 +17715,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17741,7 +17741,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17767,7 +17767,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17793,7 +17793,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17819,7 +17819,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17845,7 +17845,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17871,7 +17871,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17897,7 +17897,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17923,7 +17923,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17949,7 +17949,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17975,7 +17975,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18001,7 +18001,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18027,7 +18027,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18053,7 +18053,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18079,7 +18079,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18105,7 +18105,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18209,7 +18209,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18287,7 +18287,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18313,7 +18313,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18339,7 +18339,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18365,7 +18365,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18391,7 +18391,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18417,7 +18417,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18443,7 +18443,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18469,7 +18469,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18495,7 +18495,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18521,7 +18521,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18547,7 +18547,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18573,7 +18573,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18599,7 +18599,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18625,7 +18625,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18651,7 +18651,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18677,7 +18677,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18703,7 +18703,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18729,7 +18729,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18755,7 +18755,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18781,7 +18781,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18807,7 +18807,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18833,7 +18833,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18859,7 +18859,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18885,7 +18885,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18911,7 +18911,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18937,7 +18937,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18963,7 +18963,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18989,7 +18989,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19015,7 +19015,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19041,7 +19041,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19067,7 +19067,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19093,7 +19093,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19119,7 +19119,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19145,7 +19145,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19171,7 +19171,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19197,7 +19197,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19223,7 +19223,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19249,7 +19249,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19275,7 +19275,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19301,7 +19301,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19327,7 +19327,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19353,7 +19353,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19379,7 +19379,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19405,7 +19405,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19431,7 +19431,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19457,7 +19457,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19483,7 +19483,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19509,7 +19509,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19535,7 +19535,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19561,7 +19561,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19587,7 +19587,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19613,7 +19613,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19639,7 +19639,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19665,7 +19665,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19691,7 +19691,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19717,7 +19717,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19743,7 +19743,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19769,7 +19769,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19795,7 +19795,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19821,7 +19821,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19847,7 +19847,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19873,7 +19873,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21641,7 +21641,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70685,7 +70685,7 @@
     </row>
     <row r="2581">
       <c r="A2581" s="1" t="n">
-        <v>46079.69125</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2581" t="n">
         <v>521880</v>
@@ -70706,6 +70706,32 @@
         <v>1066</v>
       </c>
       <c r="H2581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46080.6912731481</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>789419</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>0.736000001430511</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>0.707000017166138</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>0.72299998998642</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>0.727999985218048</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H2582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
+    <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984754085541</t>
@@ -56,43 +56,43 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868479013443</t>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321182936429977</t>
+    <t xml:space="preserve">0.33589968085289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3211829662323</t>
   </si>
   <si>
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272164583206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">0.308696359395981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292998313903809</t>
+    <t xml:space="preserve">0.292998284101486</t>
   </si>
   <si>
     <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
-    <t xml:space="preserve">0.293979585170746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282830327749252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294424772262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.293979614973068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294424742460251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -143,34 +143,34 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
+    <t xml:space="preserve">0.291749387979507</t>
   </si>
   <si>
     <t xml:space="preserve">0.301114499568939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203697919846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.303166300058365</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471322774887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.301471352577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
+    <t xml:space="preserve">0.328229546546936</t>
   </si>
   <si>
     <t xml:space="preserve">0.335007637739182</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993906736374</t>
@@ -212,58 +212,58 @@
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
+    <t xml:space="preserve">0.377820700407028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
   </si>
   <si>
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353203594684601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35427314043045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.347851902246475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.373806297779083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353203564882278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354273110628128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347851932048798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359178751707077</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351419359445572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344908058643341</t>
+    <t xml:space="preserve">0.358376801013947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351419389247894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
     <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060473680496</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.352318793535233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332212656736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
+    <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15141,7 +15141,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15167,7 +15167,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15193,7 +15193,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15219,7 +15219,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15245,7 +15245,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15271,7 +15271,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15297,7 +15297,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15323,7 +15323,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15349,7 +15349,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15375,7 +15375,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15401,7 +15401,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15427,7 +15427,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15479,7 +15479,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15505,7 +15505,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15583,7 +15583,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15609,7 +15609,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15661,7 +15661,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15687,7 +15687,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15713,7 +15713,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15765,7 +15765,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15791,7 +15791,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15817,7 +15817,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15843,7 +15843,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15869,7 +15869,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15895,7 +15895,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15973,7 +15973,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15999,7 +15999,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16051,7 +16051,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16077,7 +16077,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16103,7 +16103,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16155,7 +16155,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16181,7 +16181,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16207,7 +16207,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16233,7 +16233,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16259,7 +16259,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16311,7 +16311,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16363,7 +16363,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16415,7 +16415,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16441,7 +16441,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16571,7 +16571,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16623,7 +16623,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16649,7 +16649,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16675,7 +16675,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16701,7 +16701,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16727,7 +16727,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16753,7 +16753,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16779,7 +16779,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16805,7 +16805,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16831,7 +16831,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16857,7 +16857,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16883,7 +16883,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17013,7 +17013,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17117,7 +17117,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17143,7 +17143,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17247,7 +17247,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17273,7 +17273,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17377,7 +17377,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17403,7 +17403,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17429,7 +17429,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17455,7 +17455,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17507,7 +17507,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17533,7 +17533,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17559,7 +17559,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17585,7 +17585,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17611,7 +17611,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17637,7 +17637,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17663,7 +17663,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17689,7 +17689,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17715,7 +17715,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17741,7 +17741,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17767,7 +17767,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17793,7 +17793,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17819,7 +17819,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17845,7 +17845,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17871,7 +17871,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17897,7 +17897,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17923,7 +17923,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17949,7 +17949,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17975,7 +17975,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18001,7 +18001,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18027,7 +18027,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18053,7 +18053,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18079,7 +18079,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18105,7 +18105,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18209,7 +18209,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18287,7 +18287,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18313,7 +18313,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18339,7 +18339,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18365,7 +18365,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18391,7 +18391,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18417,7 +18417,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18443,7 +18443,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18469,7 +18469,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18495,7 +18495,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18521,7 +18521,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18547,7 +18547,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18573,7 +18573,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18599,7 +18599,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18625,7 +18625,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18651,7 +18651,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18677,7 +18677,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18703,7 +18703,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18729,7 +18729,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18755,7 +18755,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18781,7 +18781,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18807,7 +18807,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18833,7 +18833,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18859,7 +18859,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18885,7 +18885,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18911,7 +18911,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18937,7 +18937,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18963,7 +18963,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18989,7 +18989,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19015,7 +19015,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19041,7 +19041,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19067,7 +19067,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19093,7 +19093,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19119,7 +19119,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19145,7 +19145,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19171,7 +19171,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19197,7 +19197,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19223,7 +19223,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19249,7 +19249,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19275,7 +19275,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19301,7 +19301,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19327,7 +19327,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19353,7 +19353,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19379,7 +19379,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19405,7 +19405,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19431,7 +19431,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19457,7 +19457,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19483,7 +19483,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19509,7 +19509,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19535,7 +19535,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19561,7 +19561,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19587,7 +19587,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19613,7 +19613,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19639,7 +19639,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19665,7 +19665,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19691,7 +19691,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19717,7 +19717,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19743,7 +19743,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19769,7 +19769,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19795,7 +19795,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19821,7 +19821,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19847,7 +19847,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19873,7 +19873,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21641,7 +21641,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70711,7 +70711,7 @@
     </row>
     <row r="2582">
       <c r="A2582" s="1" t="n">
-        <v>46080.6912731481</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2582" t="n">
         <v>789419</v>
@@ -70732,6 +70732,32 @@
         <v>1082</v>
       </c>
       <c r="H2582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46083.691087963</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>1412897</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>0.711000025272369</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>0.697000026702881</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>0.702000021934509</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>0.698000013828278</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H2583" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676603555679</t>
+    <t xml:space="preserve">0.361676573753357</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984754085541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.367920368909836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368366360664368</t>
+    <t xml:space="preserve">0.376928627490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984724283218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.367920309305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.368366330862045</t>
   </si>
   <si>
     <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366849839687347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362301081418991</t>
+    <t xml:space="preserve">0.366849809885025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36354997754097</t>
+    <t xml:space="preserve">0.363550007343292</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999319553375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.325999289751053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,28 +98,28 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196415185928</t>
+    <t xml:space="preserve">0.325196444988251</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671576023102</t>
+    <t xml:space="preserve">0.314671605825424</t>
   </si>
   <si>
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696389198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696359395981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998284101486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">0.28283029794693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288806408643723</t>
+    <t xml:space="preserve">0.2888063788414</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288984835147858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295673698186874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.290857315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288984805345535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.295673668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">0.290500432252884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302720278501511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166329860687</t>
+    <t xml:space="preserve">0.30120375752449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.302720248699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166300058365</t>
   </si>
   <si>
     <t xml:space="preserve">0.301560550928116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301471382379532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.301471322774887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328229516744614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007607936859</t>
+    <t xml:space="preserve">0.328229546546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007667541504</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
     <t xml:space="preserve">0.382993936538696</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38290473818779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820730209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350759744644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.382904767990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820670604706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350789546967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357573926448822</t>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573866844177</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376741409302</t>
+    <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
     <t xml:space="preserve">0.352579116821289</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157930612564</t>
+    <t xml:space="preserve">0.379157990217209</t>
   </si>
   <si>
     <t xml:space="preserve">0.396589815616608</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">0.345862448215485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380633920431137</t>
+    <t xml:space="preserve">0.369197160005569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.380633890628815</t>
   </si>
   <si>
     <t xml:space="preserve">0.377682030200958</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358313888311386</t>
+    <t xml:space="preserve">0.364309012889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358313918113708</t>
   </si>
   <si>
     <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
     <t xml:space="preserve">0.344387412071228</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.337838798761368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
+    <t xml:space="preserve">0.349367827177048</t>
   </si>
   <si>
     <t xml:space="preserve">0.359420835971832</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354163736104965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.352318793535233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354163706302643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
+    <t xml:space="preserve">0.341712236404419</t>
   </si>
   <si>
     <t xml:space="preserve">0.333411902189255</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">0.331843733787537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332212686538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332212656736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
     <t xml:space="preserve">0.322620838880539</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313305824995041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.312660068273544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313305795192719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.31210657954216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
@@ -560,49 +560,49 @@
     <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
+    <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.353333503007889</t>
   </si>
   <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326125353574753</t>
+    <t xml:space="preserve">0.331751465797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
     <t xml:space="preserve">0.324004560709</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
+    <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
     <t xml:space="preserve">0.32621756196022</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
+    <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
     <t xml:space="preserve">0.33129021525383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
+    <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
     <t xml:space="preserve">0.3504738509655</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385429799556732</t>
+    <t xml:space="preserve">0.37565353512764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
     <t xml:space="preserve">0.372609347105026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370931863785</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
   </si>
   <si>
     <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378604471683502</t>
+    <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
     <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
     <t xml:space="preserve">0.374085336923599</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.369935154914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
+    <t xml:space="preserve">0.436340779066086</t>
   </si>
   <si>
     <t xml:space="preserve">0.441321194171906</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
@@ -827,16 +827,16 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
   </si>
   <si>
     <t xml:space="preserve">0.60226309299469</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.636849164962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.642844259738922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.642844200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
   </si>
   <si>
     <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627165138721466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.617019772529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.627165079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.617019712924957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15141,7 +15141,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15167,7 +15167,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15193,7 +15193,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15219,7 +15219,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15245,7 +15245,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15271,7 +15271,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15297,7 +15297,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15323,7 +15323,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15349,7 +15349,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15375,7 +15375,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15401,7 +15401,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15427,7 +15427,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15479,7 +15479,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15505,7 +15505,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15583,7 +15583,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15609,7 +15609,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15661,7 +15661,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15687,7 +15687,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15713,7 +15713,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15765,7 +15765,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15791,7 +15791,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15817,7 +15817,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15843,7 +15843,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15869,7 +15869,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15895,7 +15895,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15973,7 +15973,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15999,7 +15999,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16051,7 +16051,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16077,7 +16077,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16103,7 +16103,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16155,7 +16155,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16181,7 +16181,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16207,7 +16207,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16233,7 +16233,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16259,7 +16259,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16311,7 +16311,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16363,7 +16363,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16415,7 +16415,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16441,7 +16441,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16571,7 +16571,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16623,7 +16623,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16649,7 +16649,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16675,7 +16675,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16701,7 +16701,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16727,7 +16727,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16753,7 +16753,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16779,7 +16779,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16805,7 +16805,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16831,7 +16831,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16857,7 +16857,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16883,7 +16883,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17013,7 +17013,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17117,7 +17117,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17143,7 +17143,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17247,7 +17247,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17273,7 +17273,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17377,7 +17377,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17403,7 +17403,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17429,7 +17429,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17455,7 +17455,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17507,7 +17507,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17533,7 +17533,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17559,7 +17559,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17585,7 +17585,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17611,7 +17611,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17637,7 +17637,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17663,7 +17663,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17689,7 +17689,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17715,7 +17715,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17741,7 +17741,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17767,7 +17767,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17793,7 +17793,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17819,7 +17819,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17845,7 +17845,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17871,7 +17871,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17897,7 +17897,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G550" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17923,7 +17923,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G551" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17949,7 +17949,7 @@
         <v>0.518907010555267</v>
       </c>
       <c r="G552" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17975,7 +17975,7 @@
         <v>0.531903982162476</v>
       </c>
       <c r="G553" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18001,7 +18001,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G554" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18027,7 +18027,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G555" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18053,7 +18053,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G556" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18079,7 +18079,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G557" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18105,7 +18105,7 @@
         <v>0.553900003433228</v>
       </c>
       <c r="G558" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18209,7 +18209,7 @@
         <v>0.575896024703979</v>
       </c>
       <c r="G562" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18287,7 +18287,7 @@
         <v>0.539902985095978</v>
       </c>
       <c r="G565" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18313,7 +18313,7 @@
         <v>0.5209059715271</v>
       </c>
       <c r="G566" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18339,7 +18339,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G567" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18365,7 +18365,7 @@
         <v>0.510908007621765</v>
       </c>
       <c r="G568" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18391,7 +18391,7 @@
         <v>0.496410995721817</v>
       </c>
       <c r="G569" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18417,7 +18417,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G570" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18443,7 +18443,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G571" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18469,7 +18469,7 @@
         <v>0.494410991668701</v>
       </c>
       <c r="G572" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18495,7 +18495,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G573" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18521,7 +18521,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G574" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18547,7 +18547,7 @@
         <v>0.481413006782532</v>
       </c>
       <c r="G575" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18573,7 +18573,7 @@
         <v>0.471415013074875</v>
       </c>
       <c r="G576" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18599,7 +18599,7 @@
         <v>0.474914014339447</v>
       </c>
       <c r="G577" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18625,7 +18625,7 @@
         <v>0.482412993907928</v>
       </c>
       <c r="G578" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18651,7 +18651,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G579" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18677,7 +18677,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G580" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18703,7 +18703,7 @@
         <v>0.479413986206055</v>
       </c>
       <c r="G581" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18729,7 +18729,7 @@
         <v>0.478913992643356</v>
       </c>
       <c r="G582" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18755,7 +18755,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G583" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18781,7 +18781,7 @@
         <v>0.48191300034523</v>
       </c>
       <c r="G584" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18807,7 +18807,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G585" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18833,7 +18833,7 @@
         <v>0.498910009860992</v>
       </c>
       <c r="G586" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18859,7 +18859,7 @@
         <v>0.500909984111786</v>
       </c>
       <c r="G587" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18885,7 +18885,7 @@
         <v>0.498409986495972</v>
       </c>
       <c r="G588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18911,7 +18911,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G589" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18937,7 +18937,7 @@
         <v>0.50390899181366</v>
       </c>
       <c r="G590" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18963,7 +18963,7 @@
         <v>0.492410987615585</v>
       </c>
       <c r="G591" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18989,7 +18989,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G592" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19015,7 +19015,7 @@
         <v>0.483913004398346</v>
       </c>
       <c r="G593" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19041,7 +19041,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G594" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19067,7 +19067,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G595" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19093,7 +19093,7 @@
         <v>0.490911990404129</v>
       </c>
       <c r="G596" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19119,7 +19119,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G597" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19145,7 +19145,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G598" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19171,7 +19171,7 @@
         <v>0.49141201376915</v>
       </c>
       <c r="G599" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19197,7 +19197,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G600" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19223,7 +19223,7 @@
         <v>0.479914009571075</v>
       </c>
       <c r="G601" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19249,7 +19249,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G602" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19275,7 +19275,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19301,7 +19301,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G604" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19327,7 +19327,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G605" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19353,7 +19353,7 @@
         <v>0.490411996841431</v>
       </c>
       <c r="G606" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19379,7 +19379,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G607" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19405,7 +19405,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G608" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19431,7 +19431,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G609" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19457,7 +19457,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G610" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19483,7 +19483,7 @@
         <v>0.48691201210022</v>
       </c>
       <c r="G611" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19509,7 +19509,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G612" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19535,7 +19535,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G613" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19561,7 +19561,7 @@
         <v>0.484912991523743</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19587,7 +19587,7 @@
         <v>0.485913008451462</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19613,7 +19613,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19639,7 +19639,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G617" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19665,7 +19665,7 @@
         <v>0.4949109852314</v>
       </c>
       <c r="G618" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19691,7 +19691,7 @@
         <v>0.491910994052887</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19717,7 +19717,7 @@
         <v>0.487412005662918</v>
       </c>
       <c r="G620" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19743,7 +19743,7 @@
         <v>0.489912003278732</v>
       </c>
       <c r="G621" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19769,7 +19769,7 @@
         <v>0.486411988735199</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19795,7 +19795,7 @@
         <v>0.487911999225616</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19821,7 +19821,7 @@
         <v>0.476413995027542</v>
       </c>
       <c r="G624" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19847,7 +19847,7 @@
         <v>0.47791400551796</v>
       </c>
       <c r="G625" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19873,7 +19873,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G626" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21641,7 +21641,7 @@
         <v>0.472415000200272</v>
       </c>
       <c r="G694" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -70841,7 +70841,7 @@
     </row>
     <row r="2587">
       <c r="A2587" s="1" t="n">
-        <v>46087.6910069444</v>
+        <v>46087.3333333333</v>
       </c>
       <c r="B2587" t="n">
         <v>1667026</v>
@@ -70862,6 +70862,32 @@
         <v>1036</v>
       </c>
       <c r="H2587" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" s="1" t="n">
+        <v>46090.6912847222</v>
+      </c>
+      <c r="B2588" t="n">
+        <v>2912881</v>
+      </c>
+      <c r="C2588" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="D2588" t="n">
+        <v>0.647000014781952</v>
+      </c>
+      <c r="E2588" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="G2588" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H2588" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.361676573753357</t>
+    <t xml:space="preserve">0.361676603555679</t>
   </si>
   <si>
     <t xml:space="preserve">CIR.MI</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366330862045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868508815765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366849809885025</t>
+    <t xml:space="preserve">0.368366360664368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868538618088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
     <t xml:space="preserve">0.362301051616669</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550007343292</t>
+    <t xml:space="preserve">0.363549947738647</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
+    <t xml:space="preserve">0.325999319553375</t>
   </si>
   <si>
     <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">0.324661195278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325196444988251</t>
+    <t xml:space="preserve">0.325196415185928</t>
   </si>
   <si>
     <t xml:space="preserve">0.330191254615784</t>
@@ -110,37 +110,37 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358235120773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292998284101486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.307358264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.292998313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.28283029794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857315063477</t>
+    <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295673668384552</t>
+    <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
     <t xml:space="preserve">0.291749387979507</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290054440498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500432252884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311654806137</t>
+    <t xml:space="preserve">0.29005441069603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500462055206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311625003815</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
@@ -170,34 +170,34 @@
     <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.302720248699188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303166300058365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301560550928116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471322774887</t>
+    <t xml:space="preserve">0.302720278501511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.303166329860687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301560580730438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471382379532</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512772321701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.328229546546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.335007667541504</t>
+    <t xml:space="preserve">0.313512802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.328229516744614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
     <t xml:space="preserve">0.333491951227188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358822792768478</t>
+    <t xml:space="preserve">0.358822822570801</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382904767990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377820670604706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.383350789546967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384063541889191</t>
+    <t xml:space="preserve">0.38290473818779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377820700407028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.383350759744644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.384063512086868</t>
   </si>
   <si>
     <t xml:space="preserve">0.373806297779083</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.347851902246475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357573866844177</t>
+    <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579116821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183971881866</t>
+    <t xml:space="preserve">0.352579087018967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183942079544</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">0.344908028841019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352757513523102</t>
+    <t xml:space="preserve">0.352757483720779</t>
   </si>
   <si>
     <t xml:space="preserve">0.358465969562531</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157990217209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70867,7 +70867,7 @@
     </row>
     <row r="2588">
       <c r="A2588" s="1" t="n">
-        <v>46090.6912847222</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B2588" t="n">
         <v>2912881</v>
@@ -70888,6 +70888,32 @@
         <v>1034</v>
       </c>
       <c r="H2588" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" s="1" t="n">
+        <v>46091.6911226852</v>
+      </c>
+      <c r="B2589" t="n">
+        <v>1827849</v>
+      </c>
+      <c r="C2589" t="n">
+        <v>0.695999979972839</v>
+      </c>
+      <c r="D2589" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="E2589" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H2589" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.376928627490997</t>
+    <t xml:space="preserve">0.37692865729332</t>
   </si>
   <si>
     <t xml:space="preserve">0.373984724283218</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">0.368366360664368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365868538618088</t>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">0.365690112113953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363549947738647</t>
+    <t xml:space="preserve">0.36354997754097</t>
   </si>
   <si>
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272134780884</t>
+    <t xml:space="preserve">0.321272104978561</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
+    <t xml:space="preserve">0.307358235120773</t>
   </si>
   <si>
     <t xml:space="preserve">0.308696389198303</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205820083618</t>
+    <t xml:space="preserve">0.282205849885941</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984805345535</t>
+    <t xml:space="preserve">0.288984835147858</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749387979507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
+    <t xml:space="preserve">0.29174941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
   </si>
   <si>
     <t xml:space="preserve">0.289875984191895</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">0.303166329860687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301560580730438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301471382379532</t>
+    <t xml:space="preserve">0.301560550928116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301471352577209</t>
   </si>
   <si>
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512802124023</t>
+    <t xml:space="preserve">0.313512772321701</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.382993936538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37014964222908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38290473818779</t>
+    <t xml:space="preserve">0.370149672031403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382904708385468</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">0.383350759744644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.384063512086868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373806297779083</t>
+    <t xml:space="preserve">0.384063541889191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373806327581406</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851902246475</t>
+    <t xml:space="preserve">0.347851932048798</t>
   </si>
   <si>
     <t xml:space="preserve">0.3575738966465</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292733430862</t>
+    <t xml:space="preserve">0.353292763233185</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122654914856</t>
+    <t xml:space="preserve">0.362122625112534</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">0.379157960414886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.39658984541893</t>
+    <t xml:space="preserve">0.396589815616608</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027393102646</t>
+    <t xml:space="preserve">0.370027363300323</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368920415639877</t>
+    <t xml:space="preserve">0.3689204454422</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697580337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468945741653</t>
+    <t xml:space="preserve">0.359697610139847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468975543976</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304054260254</t>
+    <t xml:space="preserve">0.351304084062576</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862418413162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.350658357143402</t>
+    <t xml:space="preserve">0.345862448215485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35065832734108</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633920431137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682000398636</t>
+    <t xml:space="preserve">0.380633890628815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682030200958</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313888311386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007754802704</t>
+    <t xml:space="preserve">0.358313918113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007725000381</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34438744187355</t>
+    <t xml:space="preserve">0.344387412071228</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328544378281</t>
+    <t xml:space="preserve">0.340328514575958</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513133764267</t>
+    <t xml:space="preserve">0.359513103961945</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848609209061</t>
+    <t xml:space="preserve">0.325848579406738</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455947399139</t>
+    <t xml:space="preserve">0.317455977201462</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805345058441</t>
+    <t xml:space="preserve">0.322805374860764</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367797374725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420865774155</t>
+    <t xml:space="preserve">0.349367827177048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420835971832</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163736104965</t>
+    <t xml:space="preserve">0.354163706302643</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712266206741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411872386932</t>
+    <t xml:space="preserve">0.341712236404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411902189255</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843703985214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212686538696</t>
+    <t xml:space="preserve">0.331843733787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212656736374</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33138245344162</t>
+    <t xml:space="preserve">0.331382423639297</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611064434052</t>
+    <t xml:space="preserve">0.315611034631729</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3264020383358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309829950333</t>
+    <t xml:space="preserve">0.326402068138123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309859752655</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620868682861</t>
+    <t xml:space="preserve">0.322620838880539</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660098075867</t>
+    <t xml:space="preserve">0.312660068273544</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31182986497879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892684221268</t>
+    <t xml:space="preserve">0.311829835176468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892654418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31219881772995</t>
+    <t xml:space="preserve">0.312198847532272</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312106609344482</t>
+    <t xml:space="preserve">0.31210657954216</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189096689224</t>
+    <t xml:space="preserve">0.324189066886902</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027339696884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071468114853</t>
+    <t xml:space="preserve">0.351027369499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071438312531</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333532810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998814821243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300079107285</t>
+    <t xml:space="preserve">0.353333503007889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998785018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300049304962</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751435995102</t>
+    <t xml:space="preserve">0.331751465797424</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004590511322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897613048553</t>
+    <t xml:space="preserve">0.324004560709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897642850876</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328246980905533</t>
+    <t xml:space="preserve">0.328247010707855</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326217591762543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344154119492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183267593384</t>
+    <t xml:space="preserve">0.32621756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344124317169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183297395706</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319116413593292</t>
+    <t xml:space="preserve">0.31911638379097</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331290245056152</t>
+    <t xml:space="preserve">0.33129021525383</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018399715424</t>
+    <t xml:space="preserve">0.344018429517746</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350473821163177</t>
+    <t xml:space="preserve">0.3504738509655</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375653505325317</t>
+    <t xml:space="preserve">0.37565353512764</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370949864387512</t>
+    <t xml:space="preserve">0.372609347105026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37094983458519</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895955324173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.381370961666107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337591171265</t>
+    <t xml:space="preserve">0.379895925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38137099146843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337561368942</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517108917236</t>
+    <t xml:space="preserve">0.372517138719559</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085307121277</t>
+    <t xml:space="preserve">0.374085336923599</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531848192215</t>
+    <t xml:space="preserve">0.373531818389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744902849197</t>
+    <t xml:space="preserve">0.394744873046875</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714637041092</t>
+    <t xml:space="preserve">0.430714666843414</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340808868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321164369583</t>
+    <t xml:space="preserve">0.436340779066086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321194171906</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145621776581</t>
+    <t xml:space="preserve">0.467145651578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47544601559639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839488267899</t>
+    <t xml:space="preserve">0.475445985794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839458465576</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099865436554</t>
+    <t xml:space="preserve">0.521099805831909</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774140834808</t>
+    <t xml:space="preserve">0.542774081230164</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345556735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495708942413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267938613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602263033390045</t>
+    <t xml:space="preserve">0.595345497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267998218536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60226309299469</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634543001651764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999317169189</t>
+    <t xml:space="preserve">0.634542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999376773834</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378193378448</t>
+    <t xml:space="preserve">0.648378133773804</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076875686646</t>
+    <t xml:space="preserve">0.640076816082001</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097331047058</t>
+    <t xml:space="preserve">0.616097271442413</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.628087520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553706169128</t>
+    <t xml:space="preserve">0.62808758020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553646564484</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863821029663</t>
+    <t xml:space="preserve">0.618863761425018</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651660442352</t>
+    <t xml:space="preserve">0.597651720046997</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585661470890045</t>
+    <t xml:space="preserve">0.5856614112854</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617480993270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.6243976354599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465383529663</t>
+    <t xml:space="preserve">0.617481052875519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.624397695064545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465443134308</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019772529602</t>
+    <t xml:space="preserve">0.617019712924957</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70893,7 +70893,7 @@
     </row>
     <row r="2589">
       <c r="A2589" s="1" t="n">
-        <v>46091.6911226852</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2589" t="n">
         <v>1827849</v>
@@ -70914,6 +70914,32 @@
         <v>1036</v>
       </c>
       <c r="H2589" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46092.6909722222</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>1252383</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>0.694000005722046</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>0.674000024795532</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H2590" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">CIR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37692865729332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373984724283218</t>
+    <t xml:space="preserve">0.376928627490997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373984754085541</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868508815765</t>
+    <t xml:space="preserve">0.368366330862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868538618088</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">0.362301051616669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365690112113953</t>
+    <t xml:space="preserve">0.36569008231163</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33589968085289</t>
+    <t xml:space="preserve">0.335899710655212</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.316634178161621</t>
+    <t xml:space="preserve">0.316634207963943</t>
   </si>
   <si>
     <t xml:space="preserve">0.325999319553375</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">0.330012857913971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321272104978561</t>
+    <t xml:space="preserve">0.321272134780884</t>
   </si>
   <si>
     <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324661195278168</t>
+    <t xml:space="preserve">0.324661165475845</t>
   </si>
   <si>
     <t xml:space="preserve">0.325196415185928</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">0.330191254615784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314671605825424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.311014920473099</t>
+    <t xml:space="preserve">0.314671576023102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.311014890670776</t>
   </si>
   <si>
     <t xml:space="preserve">0.307358235120773</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979614973068</t>
@@ -137,34 +137,34 @@
     <t xml:space="preserve">0.290857285261154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288984835147858</t>
+    <t xml:space="preserve">0.288984805345535</t>
   </si>
   <si>
     <t xml:space="preserve">0.295673698186874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29174941778183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114529371262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335544109344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289875984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29005441069603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290500462055206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.304146736860275</t>
+    <t xml:space="preserve">0.291749387979507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114499568939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335514307022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289876013994217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290054440498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.304146707057953</t>
   </si>
   <si>
     <t xml:space="preserve">0.30120375752449</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">0.313869625329971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313512772321701</t>
+    <t xml:space="preserve">0.313512802124023</t>
   </si>
   <si>
     <t xml:space="preserve">0.328229516744614</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333491951227188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822822570801</t>
+    <t xml:space="preserve">0.33349198102951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822792768478</t>
   </si>
   <si>
     <t xml:space="preserve">0.372736722230911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382904708385468</t>
+    <t xml:space="preserve">0.382993906736374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
     <t xml:space="preserve">0.377820700407028</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
+    <t xml:space="preserve">0.373806297779083</t>
   </si>
   <si>
     <t xml:space="preserve">0.353203564882278</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.35427314043045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.347851932048798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3575738966465</t>
+    <t xml:space="preserve">0.347851902246475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357573926448822</t>
   </si>
   <si>
     <t xml:space="preserve">0.359178751707077</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">0.355432868003845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358376771211624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.358376741409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">0.358465969562531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353292763233185</t>
+    <t xml:space="preserve">0.353292733430862</t>
   </si>
   <si>
     <t xml:space="preserve">0.357306271791458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362122625112534</t>
+    <t xml:space="preserve">0.362122654914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.370060443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379157960414886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.379157930612564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
+    <t xml:space="preserve">0.370027393102646</t>
   </si>
   <si>
     <t xml:space="preserve">0.37150239944458</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.373255103826523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3689204454422</t>
+    <t xml:space="preserve">0.368920415639877</t>
   </si>
   <si>
     <t xml:space="preserve">0.368828147649765</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.362925320863724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359697610139847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356468975543976</t>
+    <t xml:space="preserve">0.359697580337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356468945741653</t>
   </si>
   <si>
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35065832734108</t>
+    <t xml:space="preserve">0.345862418413162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350658357143402</t>
   </si>
   <si>
     <t xml:space="preserve">0.360620051622391</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380633890628815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.380633920431137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358313918113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.356007725000381</t>
+    <t xml:space="preserve">0.358313888311386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.356007754802704</t>
   </si>
   <si>
     <t xml:space="preserve">0.341251045465469</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">0.32372784614563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
-    <t xml:space="preserve">0.340328514575958</t>
+    <t xml:space="preserve">0.340328544378281</t>
   </si>
   <si>
     <t xml:space="preserve">0.336639612913132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359513103961945</t>
+    <t xml:space="preserve">0.359513133764267</t>
   </si>
   <si>
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
+    <t xml:space="preserve">0.322805345058441</t>
   </si>
   <si>
     <t xml:space="preserve">0.313582539558411</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">0.345033138990402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.349367827177048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.349367797374725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354163706302643</t>
+    <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
     <t xml:space="preserve">0.344756424427032</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.341619998216629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.341712236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.341712266206741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332212656736374</t>
+    <t xml:space="preserve">0.331843703985214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
     <t xml:space="preserve">0.332028180360794</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.328984975814819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331382423639297</t>
+    <t xml:space="preserve">0.33138245344162</t>
   </si>
   <si>
     <t xml:space="preserve">0.331935942173004</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
+    <t xml:space="preserve">0.315611064434052</t>
   </si>
   <si>
     <t xml:space="preserve">0.316349029541016</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402068138123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.326309859752655</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
   </si>
   <si>
     <t xml:space="preserve">0.315426558256149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">0.319761216640472</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312660068273544</t>
+    <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
     <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311829835176468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309892654418945</t>
+    <t xml:space="preserve">0.31182986497879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309892684221268</t>
   </si>
   <si>
     <t xml:space="preserve">0.312752336263657</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">0.308140903711319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.312198847532272</t>
+    <t xml:space="preserve">0.31219881772995</t>
   </si>
   <si>
     <t xml:space="preserve">0.31035390496254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31210657954216</t>
+    <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">0.310722887516022</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
+    <t xml:space="preserve">0.324189096689224</t>
   </si>
   <si>
     <t xml:space="preserve">0.338484525680542</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351027369499207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354071438312531</t>
+    <t xml:space="preserve">0.351027339696884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
@@ -581,34 +581,34 @@
     <t xml:space="preserve">0.356837958097458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353333503007889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348998785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338300049304962</t>
+    <t xml:space="preserve">0.353333532810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.348998814821243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331751465797424</t>
+    <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
     <t xml:space="preserve">0.32612532377243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324004560709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322897642850876</t>
+    <t xml:space="preserve">0.324004590511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322897613048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">0.324558079242706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31911638379097</t>
+    <t xml:space="preserve">0.319116413593292</t>
   </si>
   <si>
     <t xml:space="preserve">0.329077214002609</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.332397162914276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.342173486948013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344018429517746</t>
+    <t xml:space="preserve">0.344018399715424</t>
   </si>
   <si>
     <t xml:space="preserve">0.347891867160797</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.353241235017776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.362464070320129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.37565353512764</t>
+    <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
     <t xml:space="preserve">0.385429829359055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372609347105026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37094983458519</t>
+    <t xml:space="preserve">0.372609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370949864387512</t>
   </si>
   <si>
     <t xml:space="preserve">0.380910634994507</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">0.380357176065445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379895925521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38137099146843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
+    <t xml:space="preserve">0.379895955324173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
   </si>
   <si>
     <t xml:space="preserve">0.37860444188118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.372517138719559</t>
+    <t xml:space="preserve">0.372517108917236</t>
   </si>
   <si>
     <t xml:space="preserve">0.373162835836411</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.37574577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373531818389893</t>
+    <t xml:space="preserve">0.373531848192215</t>
   </si>
   <si>
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430714666843414</t>
+    <t xml:space="preserve">0.430714637041092</t>
   </si>
   <si>
     <t xml:space="preserve">0.433388859033585</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">0.433019906282425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.436340779066086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.436340808868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467145651578903</t>
+    <t xml:space="preserve">0.467145621776581</t>
   </si>
   <si>
     <t xml:space="preserve">0.473601996898651</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475445985794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839458465576</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
   </si>
   <si>
     <t xml:space="preserve">0.483286023139954</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">0.547846734523773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542774081230164</t>
+    <t xml:space="preserve">0.542774140834808</t>
   </si>
   <si>
     <t xml:space="preserve">0.553841829299927</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">0.589350402355194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595345497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599495649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.596267998218536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.595345556735992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599495708942413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.596267938613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.640999376773834</t>
+    <t xml:space="preserve">0.634543001651764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.640999317169189</t>
   </si>
   <si>
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
+    <t xml:space="preserve">0.648378193378448</t>
   </si>
   <si>
     <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.640076816082001</t>
+    <t xml:space="preserve">0.640076875686646</t>
   </si>
   <si>
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
+    <t xml:space="preserve">0.616097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">0.609640955924988</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62808758020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.622553646564484</t>
+    <t xml:space="preserve">0.628087520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.622553706169128</t>
   </si>
   <si>
     <t xml:space="preserve">0.617942273616791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618863761425018</t>
+    <t xml:space="preserve">0.618863821029663</t>
   </si>
   <si>
     <t xml:space="preserve">0.615174889564514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.597651720046997</t>
+    <t xml:space="preserve">0.597651660442352</t>
   </si>
   <si>
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617481052875519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.624397695064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635465443134308</t>
+    <t xml:space="preserve">0.617480993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6243976354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.635465383529663</t>
   </si>
   <si>
     <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617019712924957</t>
+    <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.609179794788361</t>
@@ -70919,7 +70919,7 @@
     </row>
     <row r="2590">
       <c r="A2590" s="1" t="n">
-        <v>46092.6909722222</v>
+        <v>46092.3333333333</v>
       </c>
       <c r="B2590" t="n">
         <v>1252383</v>
@@ -70940,6 +70940,32 @@
         <v>1054</v>
       </c>
       <c r="H2590" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46093.6910069444</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>636155</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>0.669000029563904</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>0.675999999046326</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H2591" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CIR.MI.xlsx
+++ b/data/CIR.MI.xlsx
@@ -47,25 +47,25 @@
     <t xml:space="preserve">0.376928627490997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373984754085541</t>
+    <t xml:space="preserve">0.373984724283218</t>
   </si>
   <si>
     <t xml:space="preserve">0.367920309305191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368366360664368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365868479013443</t>
+    <t xml:space="preserve">0.368366330862045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365868508815765</t>
   </si>
   <si>
     <t xml:space="preserve">0.366849839687347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362301081418991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.365690112113953</t>
+    <t xml:space="preserve">0.362301051616669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36569008231163</t>
   </si>
   <si>
     <t xml:space="preserve">0.36354997754097</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">0.358198344707489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.335899710655212</t>
+    <t xml:space="preserve">0.33589968085289</t>
   </si>
   <si>
     <t xml:space="preserve">0.321182936429977</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.316634178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325999289751053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330012828111649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321272164583206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321450561285019</t>
+    <t xml:space="preserve">0.325999319553375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330012857913971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321272134780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.321450531482697</t>
   </si>
   <si>
     <t xml:space="preserve">0.324661195278168</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">0.311014920473099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.307358264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.308696359395981</t>
+    <t xml:space="preserve">0.307358235120773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.308696389198303</t>
   </si>
   <si>
     <t xml:space="preserve">0.292998313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282205849885941</t>
+    <t xml:space="preserve">0.282205820083618</t>
   </si>
   <si>
     <t xml:space="preserve">0.293979585170746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.282830327749252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2888063788414</t>
+    <t xml:space="preserve">0.282830268144608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288806408643723</t>
   </si>
   <si>
     <t xml:space="preserve">0.294424772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290857285261154</t>
+    <t xml:space="preserve">0.290857315063477</t>
   </si>
   <si>
     <t xml:space="preserve">0.288984805345535</t>
@@ -143,31 +143,31 @@
     <t xml:space="preserve">0.295673668384552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.291749358177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.301114499568939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.294335514307022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.289876013994217</t>
+    <t xml:space="preserve">0.29174941778183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.301114529371262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.294335544109344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289875984191895</t>
   </si>
   <si>
     <t xml:space="preserve">0.290054440498352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290500491857529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300311625003815</t>
+    <t xml:space="preserve">0.290500432252884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300311654806137</t>
   </si>
   <si>
     <t xml:space="preserve">0.304146736860275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.301203697919846</t>
+    <t xml:space="preserve">0.30120375752449</t>
   </si>
   <si>
     <t xml:space="preserve">0.302720278501511</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.301471322774887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313869595527649</t>
+    <t xml:space="preserve">0.313869655132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.313512772321701</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">0.335007637739182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333491951227188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358822822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372736692428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.382993906736374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370149672031403</t>
+    <t xml:space="preserve">0.33349198102951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358822792768478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372736722230911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.382993936538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37014964222908</t>
   </si>
   <si>
     <t xml:space="preserve">0.38290473818779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377820730209351</t>
+    <t xml:space="preserve">0.377820700407028</t>
   </si>
   <si>
     <t xml:space="preserve">0.383350759744644</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">0.384063541889191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373806327581406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353203594684601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35427314043045</t>
+    <t xml:space="preserve">0.373806297779083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353203564882278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354273110628128</t>
   </si>
   <si>
     <t xml:space="preserve">0.347851902246475</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.3575738966465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359178721904755</t>
+    <t xml:space="preserve">0.359178781509399</t>
   </si>
   <si>
     <t xml:space="preserve">0.355432868003845</t>
@@ -245,40 +245,40 @@
     <t xml:space="preserve">0.358376771211624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.352579087018967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.354183942079544</t>
+    <t xml:space="preserve">0.352579116821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.354183971881866</t>
   </si>
   <si>
     <t xml:space="preserve">0.351419359445572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.344908058643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.352757483720779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.358465999364853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353292763233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.357306271791458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.362122625112534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.370060473680496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.379157930612564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.396589815616608</t>
+    <t xml:space="preserve">0.344908028841019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352757513523102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.358465969562531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353292733430862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.357306241989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.362122654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370060443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.379157960414886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39658984541893</t>
   </si>
   <si>
     <t xml:space="preserve">0.37814325094223</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">0.372701615095139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370027363300323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371502429246902</t>
+    <t xml:space="preserve">0.370027393102646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37150239944458</t>
   </si>
   <si>
     <t xml:space="preserve">0.373255103826523</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">0.356930196285248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351304084062576</t>
+    <t xml:space="preserve">0.351304054260254</t>
   </si>
   <si>
     <t xml:space="preserve">0.346692651510239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345862448215485</t>
+    <t xml:space="preserve">0.345862418413162</t>
   </si>
   <si>
     <t xml:space="preserve">0.350658357143402</t>
@@ -332,40 +332,40 @@
     <t xml:space="preserve">0.360620051622391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369197130203247</t>
+    <t xml:space="preserve">0.369197160005569</t>
   </si>
   <si>
     <t xml:space="preserve">0.380633920431137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377682030200958</t>
+    <t xml:space="preserve">0.377682000398636</t>
   </si>
   <si>
     <t xml:space="preserve">0.362187325954437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36430898308754</t>
+    <t xml:space="preserve">0.364309012889862</t>
   </si>
   <si>
     <t xml:space="preserve">0.358313888311386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356007725000381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341251015663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.323727816343307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.344387412071228</t>
+    <t xml:space="preserve">0.356007754802704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.341251045465469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32372784614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.34438744187355</t>
   </si>
   <si>
     <t xml:space="preserve">0.325571835041046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33783882856369</t>
+    <t xml:space="preserve">0.337838798761368</t>
   </si>
   <si>
     <t xml:space="preserve">0.340328544378281</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">0.317548245191574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325848579406738</t>
+    <t xml:space="preserve">0.325848609209061</t>
   </si>
   <si>
     <t xml:space="preserve">0.320130199193954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317455977201462</t>
+    <t xml:space="preserve">0.317455947399139</t>
   </si>
   <si>
     <t xml:space="preserve">0.323082119226456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322805374860764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313582569360733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.312567800283432</t>
+    <t xml:space="preserve">0.322805345058441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.313582539558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.312567830085754</t>
   </si>
   <si>
     <t xml:space="preserve">0.329169452190399</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">0.349367797374725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.359420835971832</t>
+    <t xml:space="preserve">0.359420865774155</t>
   </si>
   <si>
     <t xml:space="preserve">0.35895961523056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350935101509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353886961936951</t>
+    <t xml:space="preserve">0.350935071706772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353886932134628</t>
   </si>
   <si>
     <t xml:space="preserve">0.357114672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35231876373291</t>
+    <t xml:space="preserve">0.352318793535233</t>
   </si>
   <si>
     <t xml:space="preserve">0.354163736104965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34475639462471</t>
+    <t xml:space="preserve">0.344756424427032</t>
   </si>
   <si>
     <t xml:space="preserve">0.35222652554512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357760369777679</t>
+    <t xml:space="preserve">0.357760399580002</t>
   </si>
   <si>
     <t xml:space="preserve">0.341619998216629</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.341712266206741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333411902189255</t>
+    <t xml:space="preserve">0.333411872386932</t>
   </si>
   <si>
     <t xml:space="preserve">0.335532665252686</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">0.333135157823563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331843733787537</t>
+    <t xml:space="preserve">0.331843703985214</t>
   </si>
   <si>
     <t xml:space="preserve">0.332212686538696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332028150558472</t>
+    <t xml:space="preserve">0.332028180360794</t>
   </si>
   <si>
     <t xml:space="preserve">0.328984975814819</t>
@@ -482,34 +482,34 @@
     <t xml:space="preserve">0.321790635585785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.315611034631729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.316348999738693</t>
+    <t xml:space="preserve">0.315611064434052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.316349029541016</t>
   </si>
   <si>
     <t xml:space="preserve">0.308417648077011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326402097940445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32630980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315426528453827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322620838880539</t>
+    <t xml:space="preserve">0.3264020383358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326309829950333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315426558256149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322620868682861</t>
   </si>
   <si>
     <t xml:space="preserve">0.318470686674118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320960432291031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.315518826246262</t>
+    <t xml:space="preserve">0.320960402488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.315518796443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.315242052078247</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">0.312660098075867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.313305824995041</t>
+    <t xml:space="preserve">0.313305795192719</t>
   </si>
   <si>
     <t xml:space="preserve">0.31182986497879</t>
@@ -548,46 +548,46 @@
     <t xml:space="preserve">0.312106609344482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310722917318344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.310907363891602</t>
+    <t xml:space="preserve">0.310722887516022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.310907393693924</t>
   </si>
   <si>
     <t xml:space="preserve">0.32354336977005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324189066886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.338484555482864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.340605288743973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343833953142166</t>
+    <t xml:space="preserve">0.324189096689224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.338484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.340605318546295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.343833923339844</t>
   </si>
   <si>
     <t xml:space="preserve">0.351027339696884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.354071497917175</t>
+    <t xml:space="preserve">0.354071468114853</t>
   </si>
   <si>
     <t xml:space="preserve">0.354440450668335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356837928295135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.353333503007889</t>
+    <t xml:space="preserve">0.356837958097458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.353333532810211</t>
   </si>
   <si>
     <t xml:space="preserve">0.348998814821243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830001950264</t>
+    <t xml:space="preserve">0.338300079107285</t>
   </si>
   <si>
     <t xml:space="preserve">0.334242105484009</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">0.331751435995102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326125353574753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.324004560709</t>
+    <t xml:space="preserve">0.32612532377243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.324004590511322</t>
   </si>
   <si>
     <t xml:space="preserve">0.322897613048553</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">0.325387358665466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328247010707855</t>
+    <t xml:space="preserve">0.328246980905533</t>
   </si>
   <si>
     <t xml:space="preserve">0.325110614299774</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">0.328062504529953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324558049440384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32621756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.322344124317169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.330183297395706</t>
+    <t xml:space="preserve">0.324558079242706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.326217591762543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.322344154119492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.330183267593384</t>
   </si>
   <si>
     <t xml:space="preserve">0.325664073228836</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.329077214002609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.332397192716599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33129021525383</t>
+    <t xml:space="preserve">0.332397162914276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.331290245056152</t>
   </si>
   <si>
     <t xml:space="preserve">0.334334373474121</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">0.347891867160797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353241264820099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.3504738509655</t>
+    <t xml:space="preserve">0.353241235017776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.350473821163177</t>
   </si>
   <si>
     <t xml:space="preserve">0.355086177587509</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.350105792284012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351396292448044</t>
+    <t xml:space="preserve">0.351396322250366</t>
   </si>
   <si>
     <t xml:space="preserve">0.355547398328781</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">0.375653505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385429799556732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372609347105026</t>
+    <t xml:space="preserve">0.385429829359055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372609376907349</t>
   </si>
   <si>
     <t xml:space="preserve">0.370949864387512</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">0.380910634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380449414253235</t>
+    <t xml:space="preserve">0.380449384450912</t>
   </si>
   <si>
     <t xml:space="preserve">0.379342466592789</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">0.379895955324173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.381370931863785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.385337561368942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.378604471683502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.372517138719559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373162865638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.375745743513107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.374085336923599</t>
+    <t xml:space="preserve">0.381370961666107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.385337591171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37860444188118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.372517108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373162835836411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37574577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.374085307121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.371225655078888</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.369750648736954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.369935125112534</t>
+    <t xml:space="preserve">0.369935154914856</t>
   </si>
   <si>
     <t xml:space="preserve">0.373531848192215</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">0.379803687334061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.394744873046875</t>
+    <t xml:space="preserve">0.394744902849197</t>
   </si>
   <si>
     <t xml:space="preserve">0.42518076300621</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">0.432927638292313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433757841587067</t>
+    <t xml:space="preserve">0.433757871389389</t>
   </si>
   <si>
     <t xml:space="preserve">0.433019906282425</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">0.436340808868408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441321194171906</t>
+    <t xml:space="preserve">0.441321164369583</t>
   </si>
   <si>
     <t xml:space="preserve">0.453403651714325</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">0.502654194831848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475446045398712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.464839428663254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.483286052942276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515105605125427</t>
+    <t xml:space="preserve">0.47544601559639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.464839488267899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.483286023139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515105545520782</t>
   </si>
   <si>
     <t xml:space="preserve">0.512799441814423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531245172023773</t>
+    <t xml:space="preserve">0.531245112419128</t>
   </si>
   <si>
     <t xml:space="preserve">0.511877000331879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521099805831909</t>
+    <t xml:space="preserve">0.521099865436554</t>
   </si>
   <si>
     <t xml:space="preserve">0.535396218299866</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">0.553841829299927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557991981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555225610733032</t>
+    <t xml:space="preserve">0.557992041110992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555225551128387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579205095767975</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">0.596267938613892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60226309299469</t>
+    <t xml:space="preserve">0.602263033390045</t>
   </si>
   <si>
     <t xml:space="preserve">0.604107081890106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61010217666626</t>
+    <t xml:space="preserve">0.610102236270905</t>
   </si>
   <si>
     <t xml:space="preserve">0.626242637634277</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">0.610563457012177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636849105358124</t>
+    <t xml:space="preserve">0.636849164962769</t>
   </si>
   <si>
     <t xml:space="preserve">0.634543001651764</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.654833555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648378133773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.642844259738922</t>
+    <t xml:space="preserve">0.648378193378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.642844200134277</t>
   </si>
   <si>
     <t xml:space="preserve">0.640076875686646</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">0.635004222393036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616097271442413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609641015529633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.602724373340607</t>
+    <t xml:space="preserve">0.616097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609640955924988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.602724313735962</t>
   </si>
   <si>
     <t xml:space="preserve">0.628087520599365</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">0.584738969802856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5856614112854</t>
+    <t xml:space="preserve">0.585661470890045</t>
   </si>
   <si>
     <t xml:space="preserve">0.607796967029572</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">0.6243976354599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635465443134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.627165138721466</t>
+    <t xml:space="preserve">0.635465383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.627165079116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.617019772529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.609179735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.612408339977264</t>
+    <t xml:space="preserve">0.609179794788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.612408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">0.603645861148834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608829379081726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61307030916214</t>
+    <t xml:space="preserve">0.608829319477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.613070249557495</t>
   </si>
   <si>
     <t xml:space="preserve">0.592336177825928</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">0.584325730800629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.581969201564789</t>
+    <t xml:space="preserve">0.581969141960144</t>
   </si>
   <si>
     <t xml:space="preserve">0.581026494503021</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">0.579612612724304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.57395875453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.580555260181427</t>
+    <t xml:space="preserve">0.573958694934845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.587152659893036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.580555200576782</t>
   </si>
   <si>
     <t xml:space="preserve">0.574429094791412</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546627163887024</t>
+    <t xml:space="preserve">0.546627104282379</t>
   </si>
   <si>
     <t xml:space="preserve">0.545213222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547569811344147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533903539180756</t>
+    <t xml:space="preserve">0.547569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5339035987854</t>
   </si>
   <si>
     <t xml:space="preserve">0.524950444698334</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">0.531076610088348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533432245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.544741868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.550396740436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.540972352027893</t>
+    <t xml:space="preserve">0.533432185649872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.544741928577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.550396800041199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.540972292423248</t>
   </si>
   <si>
     <t xml:space="preserve">0.556051552295685</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">0.543327927589417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.539087057113647</t>
+    <t xml:space="preserve">0.539086997509003</t>
   </si>
   <si>
     <t xml:space="preserve">0.532960891723633</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">0.54002970457077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555108964443207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.555580198764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559349894523621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.548040091991425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.536731421947479</t>
+    <t xml:space="preserve">0.555108904838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.555580258369446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.559349834918976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.548040151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536731362342834</t>
   </si>
   <si>
     <t xml:space="preserve">0.529191315174103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538615763187408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.549454092979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.542386293411255</t>
+    <t xml:space="preserve">0.538615703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.549454033374786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54238623380661</t>
   </si>
   <si>
     <t xml:space="preserve">0.538144409656525</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">0.526834726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.527777373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52447909116745</t>
+    <t xml:space="preserve">0.527777314186096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.524479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">0.525421738624573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523065149784088</t>
+    <t xml:space="preserve">0.523065209388733</t>
   </si>
   <si>
     <t xml:space="preserve">0.524007797241211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521180927753448</t>
+    <t xml:space="preserve">0.521180868148804</t>
   </si>
   <si>
     <t xml:space="preserve">0.520238220691681</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">0.526364326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528720021247864</t>
+    <t xml:space="preserve">0.528720080852509</t>
   </si>
   <si>
     <t xml:space="preserve">0.557936787605286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560292482376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.556994140148163</t>
+    <t xml:space="preserve">0.560292422771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.556994199752808</t>
   </si>
   <si>
     <t xml:space="preserve">0.56170642375946</t>
@@ -1148,25 +1148,28 @@
     <t xml:space="preserve">0.576785624027252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592807531356812</t>
+    <t xml:space="preserve">0.603645801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.592807471752167</t>
   </si>
   <si>
     <t xml:space="preserve">0.59751969575882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596577048301697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.595163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.609772026538849</t>
+    <t xml:space="preserve">0.596577107906342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.59516316652298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.609772086143494</t>
   </si>
   <si>
     <t xml:space="preserve">0.599404990673065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599876224994659</t>
+    <t xml:space="preserve">0.599876284599304</t>
   </si>
   <si>
     <t xml:space="preserve">0.603174567222595</t>
@@ -1184,10 +1187,10 @@
     <t xml:space="preserve">0.580083906650543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.578670859336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.565947294235229</t>
+    <t xml:space="preserve">0.578670918941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.565947234630585</t>
   </si>
   <si>
     <t xml:space="preserve">0.554166316986084</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.570188164710999</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564533352851868</t>
+    <t xml:space="preserve">0.564533293247223</t>
   </si>
   <si>
     <t xml:space="preserve">0.560763776302338</t>
@@ -1214,7 +1217,7 @@
     <t xml:space="preserve">0.550868034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53767317533493</t>
+    <t xml:space="preserve">0.537673115730286</t>
   </si>
   <si>
     <t xml:space="preserve">0.527306079864502</t>
@@ -1229,7 +1232,7 @@
     <t xml:space="preserve">0.51458340883255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506100714206696</t>
+    <t xml:space="preserve">0.506100654602051</t>
   </si>
   <si>
     <t xml:space="preserve">0.505629360675812</t>
@@ -1250,16 +1253,16 @@
     <t xml:space="preserve">0.531547844409943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543799221515656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.515997350215912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.488194525241852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.492906719446182</t>
+    <t xml:space="preserve">0.5437992811203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515997409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.488194495439529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49290668964386</t>
   </si>
   <si>
     <t xml:space="preserve">0.510342478752136</t>
@@ -1268,7 +1271,7 @@
     <t xml:space="preserve">0.513640820980072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51222687959671</t>
+    <t xml:space="preserve">0.512226819992065</t>
   </si>
   <si>
     <t xml:space="preserve">0.507985949516296</t>
@@ -1277,7 +1280,7 @@
     <t xml:space="preserve">0.525893032550812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545684456825256</t>
+    <t xml:space="preserve">0.545684516429901</t>
   </si>
   <si>
     <t xml:space="preserve">0.552281975746155</t>
@@ -1292,19 +1295,19 @@
     <t xml:space="preserve">0.530605256557465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518352925777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.493849337100983</t>
+    <t xml:space="preserve">0.51835298538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49384930729866</t>
   </si>
   <si>
     <t xml:space="preserve">0.503273725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.490078747272491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.482539623975754</t>
+    <t xml:space="preserve">0.490078777074814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.482539653778076</t>
   </si>
   <si>
     <t xml:space="preserve">0.476884812116623</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">0.465103834867477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.478770077228546</t>
+    <t xml:space="preserve">0.478770047426224</t>
   </si>
   <si>
     <t xml:space="preserve">0.491964101791382</t>
@@ -1322,13 +1325,13 @@
     <t xml:space="preserve">0.496676236391068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.487251847982407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491021424531937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48913711309433</t>
+    <t xml:space="preserve">0.487251818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491021364927292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.489137142896652</t>
   </si>
   <si>
     <t xml:space="preserve">0.501388430595398</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">0.481597036123276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467931717634201</t>
+    <t xml:space="preserve">0.467931687831879</t>
   </si>
   <si>
     <t xml:space="preserve">0.462276875972748</t>
@@ -1379,7 +1382,7 @@
     <t xml:space="preserve">0.454265475273132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451909840106964</t>
+    <t xml:space="preserve">0.451909810304642</t>
   </si>
   <si>
     <t xml:space="preserve">0.451438516378403</t>
@@ -1397,7 +1400,7 @@
     <t xml:space="preserve">0.47217258810997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.469816029071808</t>
+    <t xml:space="preserve">0.469815999269485</t>
   </si>
   <si>
     <t xml:space="preserve">0.4749995470047</t>
@@ -1406,22 +1409,22 @@
     <t xml:space="preserve">0.464161187410355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.466517746448517</t>
+    <t xml:space="preserve">0.466517776250839</t>
   </si>
   <si>
     <t xml:space="preserve">0.457093328237534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458977699279785</t>
+    <t xml:space="preserve">0.458977669477463</t>
   </si>
   <si>
     <t xml:space="preserve">0.462748199701309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458035975694656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506375551224</t>
+    <t xml:space="preserve">0.458036005496979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.463689863681793</t>
@@ -1434,9 +1437,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.463843464851379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.458506345748901</t>
   </si>
   <si>
     <t xml:space="preserve">0.455594688653946</t>
@@ -15150,7 +15150,7 @@
         <v>0.64038497209549</v>
       </c>
       <c r="G444" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15176,7 +15176,7 @@
         <v>0.628886997699738</v>
       </c>
       <c r="G445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15202,7 +15202,7 @@
         <v>0.633885979652405</v>
       </c>
       <c r="G446" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15228,7 +15228,7 @@
         <v>0.632885992527008</v>
       </c>
       <c r="G447" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15254,7 +15254,7 @@
         <v>0.631385982036591</v>
       </c>
       <c r="G448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15280,7 +15280,7 @@
         <v>0.646884024143219</v>
       </c>
       <c r="G449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15306,7 +15306,7 @@
         <v>0.635886013507843</v>
       </c>
       <c r="G450" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15332,7 +15332,7 @@
         <v>0.636385977268219</v>
       </c>
       <c r="G451" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15358,7 +15358,7 @@
         <v>0.639885008335114</v>
       </c>
       <c r="G452" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15384,7 +15384,7 @@
         <v>0.620887994766235</v>
       </c>
       <c r="G453" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15410,7 +15410,7 @@
         <v>0.625388026237488</v>
       </c>
       <c r="G454" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15436,7 +15436,7 @@
         <v>0.624888002872467</v>
       </c>
       <c r="G455" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15488,7 +15488,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G457" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15514,7 +15514,7 @@
         <v>0.615388989448547</v>
       </c>
       <c r="G458" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15592,7 +15592,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G461" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15618,7 +15618,7 @@
         <v>0.600391983985901</v>
       </c>
       <c r="G462" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15670,7 +15670,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G464" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15696,7 +15696,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G465" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15722,7 +15722,7 @@
         <v>0.598891973495483</v>
       </c>
       <c r="G466" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15774,7 +15774,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G468" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15800,7 +15800,7 @@
         <v>0.613889992237091</v>
       </c>
       <c r="G469" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15826,7 +15826,7 @@
         <v>0.610889971256256</v>
       </c>
       <c r="G470" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15852,7 +15852,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G471" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15878,7 +15878,7 @@
         <v>0.590394020080566</v>
       </c>
       <c r="G472" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15904,7 +15904,7 @@
         <v>0.594892978668213</v>
       </c>
       <c r="G473" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15982,7 +15982,7 @@
         <v>0.584394991397858</v>
       </c>
       <c r="G476" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16008,7 +16008,7 @@
         <v>0.570397019386292</v>
       </c>
       <c r="G477" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16060,7 +16060,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G479" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16086,7 +16086,7 @@
         <v>0.53440397977829</v>
       </c>
       <c r="G480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16112,7 +16112,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G481" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16164,7 +16164,7 @@
         <v>0.545902013778687</v>
       </c>
       <c r="G483" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16190,7 +16190,7 @@
         <v>0.536903023719788</v>
       </c>
       <c r="G484" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16216,7 +16216,7 @@
         <v>0.536403000354767</v>
       </c>
       <c r="G485" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16242,7 +16242,7 @@
         <v>0.540403008460999</v>
       </c>
       <c r="G486" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16268,7 +16268,7 @@
         <v>0.555400013923645</v>
       </c>
       <c r="G487" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16320,7 +16320,7 @@
         <v>0.564898014068604</v>
       </c>
       <c r="G489" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16372,7 +16372,7 @@
         <v>0.567897975444794</v>
       </c>
       <c r="G491" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16424,7 +16424,7 @@
         <v>0.563898980617523</v>
       </c>
       <c r="G493" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16450,7 +16450,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G494" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16580,7 +16580,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G499" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16632,7 +16632,7 @@
         <v>0.559399008750916</v>
       </c>
       <c r="G501" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16658,7 +16658,7 @@
         <v>0.547402024269104</v>
       </c>
       <c r="G502" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16684,7 +16684,7 @@
         <v>0.517907023429871</v>
       </c>
       <c r="G503" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16710,7 +16710,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G504" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16736,7 +16736,7 @@
         <v>0.532404005527496</v>
       </c>
       <c r="G505" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16762,7 +16762,7 @@
         <v>0.541402995586395</v>
       </c>
       <c r="G506" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16788,7 +16788,7 @@
         <v>0.54490202665329</v>
       </c>
       <c r="G507" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16814,7 +16814,7 @@
         <v>0.543402016162872</v>
       </c>
       <c r="G508" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16840,7 +16840,7 @@
         <v>0.538902997970581</v>
       </c>
       <c r="G509" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16866,7 +16866,7 @@
         <v>0.557900011539459</v>
       </c>
       <c r="G510" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16892,7 +16892,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G511" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17022,7 +17022,7 @@
         <v>0.585895001888275</v>
       </c>
       <c r="G516" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17126,7 +17126,7 @@
         <v>0.587894022464752</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17152,7 +17152,7 @@
         <v>0.586893975734711</v>
       </c>
       <c r="G521" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17256,7 +17256,7 @@
         <v>0.576896011829376</v>
       </c>
       <c r="G525" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17282,7 +17282,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17386,7 +17386,7 @@
         <v>0.604891002178192</v>
       </c>
       <c r="G530" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17412,7 +17412,7 @@
         <v>0.599892020225525</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17438,7 +17438,7 @@
         <v>0.57889598608017</v>
       </c>
       <c r="G532" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17464,7 +17464,7 @@
         <v>0.581894993782043</v>
       </c>
       <c r="G533" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17516,7 +17516,7 @@
         <v>0.562898993492126</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17542,7 +17542,7 @@
         <v>0.549901008605957</v>
       </c>
       <c r="G536" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17568,7 +17568,7 @@
         <v>0.523905992507935</v>
       </c>
       <c r="G537" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17594,7 +17594,7 @@
         <v>0.533904016017914</v>
       </c>
       <c r="G538" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17620,7 +17620,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G539" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17646,7 +17646,7 @@
         <v>0.511907994747162</v>
       </c>
       <c r="G540" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17672,7 +17672,7 @@
         <v>0.505909025669098</v>
       </c>
       <c r="G541" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17698,7 +17698,7 @@
         <v>0.493411004543304</v>
       </c>
       <c r="G542" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17724,7 +17724,7 @@
         <v>0.507908999919891</v>
       </c>
       <c r="G543" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17750,7 +17750,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G544" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17776,7 +17776,7 @@
         <v>0.522906005382538</v>
       </c>
       <c r="G545" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17802,7 +17802,7 @@
         <v>0.521906018257141</v>
       </c>
       <c r="G546" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17828,7 +17828,7 @@
         <v>0.526905000209808</v>
       </c>
       <c r="G547" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17854,7 +17854,7 @@
         <v>0.519905984401703</v>
       </c>
       <c r="G548" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17880,7 +17880,7 @@
         <v>0.516906976699829</v>
       </c>
       <c r="G549" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H549" t="s">
         <